--- a/src/test/resources/manual-testcases.xlsx
+++ b/src/test/resources/manual-testcases.xlsx
@@ -2,15 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Login" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departments" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="3">
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -659,7 +675,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O240"/>
+  <dimension ref="A1:P240"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -784,6 +800,9 @@
           <t>Test Steps</t>
         </is>
       </c>
+      <c r="P3" t="s" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -858,6 +877,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P5" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -915,6 +937,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P6" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -972,6 +997,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P7" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -1029,6 +1057,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P8" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -1086,6 +1117,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P9" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -1143,6 +1177,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P10" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n"/>
@@ -1200,6 +1237,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P11" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -1257,6 +1297,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P12" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -1314,6 +1357,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P13" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -1371,6 +1417,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P14" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -1428,6 +1477,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P15" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -1485,6 +1537,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P16" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -1542,6 +1597,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P17" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -1599,6 +1657,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P18" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1656,6 +1717,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P19" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1713,6 +1777,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P20" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -1770,6 +1837,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P21" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -1827,6 +1897,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P22" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -1884,6 +1957,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P23" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="n"/>
@@ -1941,6 +2017,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P24" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -1998,6 +2077,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P25" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -2055,6 +2137,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P26" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -2112,6 +2197,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P27" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -2169,6 +2257,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P28" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -2226,6 +2317,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P29" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -2283,6 +2377,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P30" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -2340,6 +2437,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P31" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -2397,6 +2497,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P32" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -2454,6 +2557,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P33" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -2511,6 +2617,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P34" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -2568,6 +2677,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P35" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -2625,6 +2737,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P36" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -2682,6 +2797,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P37" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -2739,6 +2857,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P38" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -2797,6 +2918,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P39" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -2855,6 +2979,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P40" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -2912,6 +3039,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P41" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -2969,6 +3099,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P42" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -3026,6 +3159,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P43" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -3083,6 +3219,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P44" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -3140,6 +3279,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P45" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -3197,6 +3339,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P46" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -3254,6 +3399,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P47" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -3315,6 +3463,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P48" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -3376,6 +3527,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P49" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -3437,6 +3591,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P50" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -3498,6 +3655,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P51" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -3559,6 +3719,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P52" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -3620,6 +3783,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P53" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -3681,6 +3847,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P54" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -3742,6 +3911,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P55" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -3802,6 +3974,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P56" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3877,6 +4052,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P58" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="20" t="n"/>
@@ -3934,6 +4112,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P59" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="20" t="n"/>
@@ -3991,6 +4172,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P60" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="20" t="n"/>
@@ -4048,6 +4232,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P61" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="20" t="n"/>
@@ -4105,6 +4292,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P62" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="20" t="n"/>
@@ -4162,6 +4352,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P63" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="20" t="n"/>
@@ -4219,6 +4412,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P64" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="20" t="n"/>
@@ -4276,6 +4472,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P65" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="20" t="n"/>
@@ -4333,6 +4532,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P66" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="20" t="n"/>
@@ -4390,6 +4592,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P67" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="20" t="n"/>
@@ -4447,6 +4652,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P68" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="20" t="n"/>
@@ -4504,6 +4712,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P69" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="20" t="n"/>
@@ -4561,6 +4772,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P70" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="20" t="n"/>
@@ -4618,6 +4832,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P71" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="20" t="n"/>
@@ -4675,6 +4892,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P72" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="20" t="n"/>
@@ -4732,6 +4952,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P73" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="20" t="n"/>
@@ -4789,6 +5012,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P74" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="20" t="n"/>
@@ -4846,6 +5072,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P75" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="20" t="n"/>
@@ -4903,6 +5132,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P76" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="20" t="n"/>
@@ -4960,6 +5192,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P77" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="20" t="n"/>
@@ -5017,6 +5252,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P78" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="20" t="n"/>
@@ -5074,6 +5312,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P79" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="20" t="n"/>
@@ -5131,6 +5372,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P80" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="20" t="n"/>
@@ -5188,6 +5432,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P81" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="20" t="n"/>
@@ -5245,6 +5492,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P82" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -5302,6 +5552,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P83" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -5359,6 +5612,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P84" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -5416,6 +5672,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P85" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="20" t="n"/>
@@ -5474,6 +5733,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P86" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="n"/>
@@ -5532,6 +5794,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P87" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -5589,6 +5854,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P88" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -5646,6 +5914,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P89" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -5703,6 +5974,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P90" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -5760,6 +6034,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P91" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -5817,6 +6094,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P92" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
@@ -5874,6 +6154,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P93" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -5931,6 +6214,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P94" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -5988,6 +6274,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P95" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -6045,6 +6334,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P96" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -6101,6 +6393,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P97" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -6151,6 +6446,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P98" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -6200,6 +6498,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P99" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -6249,6 +6550,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P100" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -6298,6 +6602,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P101" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -6347,6 +6654,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P102" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -6396,6 +6706,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P103" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -6445,6 +6758,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P104" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
@@ -6494,6 +6810,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P105" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -6543,6 +6862,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P106" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -6592,6 +6914,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P107" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -6641,6 +6966,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P108" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -6689,6 +7017,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P109" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -6737,6 +7068,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P110" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -6784,6 +7118,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P111" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -6831,6 +7168,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P112" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -6878,6 +7218,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P113" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -6925,6 +7268,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P114" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -6972,6 +7318,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P115" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -7019,6 +7368,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P116" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
@@ -7066,6 +7418,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P117" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -7113,6 +7468,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P118" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -7160,6 +7518,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P119" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -7207,6 +7568,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P120" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -7254,6 +7618,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P121" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -7301,6 +7668,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P122" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -7348,6 +7718,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P123" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -7395,6 +7768,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P124" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -7442,6 +7818,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P125" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -7489,6 +7868,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P126" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -7536,6 +7918,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P127" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -7583,6 +7968,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P128" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
@@ -7630,6 +8018,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P129" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -7677,6 +8068,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P130" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -7724,6 +8118,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P131" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -7771,6 +8168,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P132" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -7818,6 +8218,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P133" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -7865,6 +8268,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P134" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -7911,6 +8317,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P135" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -7980,6 +8389,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P137" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="39" t="n"/>
@@ -8031,6 +8443,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P138" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="39" t="n"/>
@@ -8082,6 +8497,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P139" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -8133,6 +8551,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P140" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
@@ -8184,6 +8605,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P141" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -8235,6 +8659,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P142" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -8286,6 +8713,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P143" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -8337,6 +8767,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P144" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -8388,6 +8821,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P145" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -8439,6 +8875,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P146" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -8490,6 +8929,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P147" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -8541,6 +8983,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P148" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -8592,6 +9037,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P149" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -8643,6 +9091,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P150" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -8694,6 +9145,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P151" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -8745,6 +9199,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P152" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
@@ -8796,6 +9253,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P153" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -8847,6 +9307,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P154" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -8898,6 +9361,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P155" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -8948,6 +9414,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P156" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -9027,6 +9496,9 @@
  2. Click on it</t>
         </is>
       </c>
+      <c r="P158" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="62" t="n"/>
@@ -9085,6 +9557,9 @@
           <t>1. Click 'My Profile' from the dropdown</t>
         </is>
       </c>
+      <c r="P159" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="62" t="n"/>
@@ -9143,6 +9618,9 @@
  2. Press Enter</t>
         </is>
       </c>
+      <c r="P160" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="62" t="n"/>
@@ -9200,6 +9678,9 @@
           <t>1. Navigate directly to uat.visdum.com/profile</t>
         </is>
       </c>
+      <c r="P161" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="62" t="n"/>
@@ -9257,6 +9738,9 @@
           <t>1. Click the '←' back arrow next to the 'Profile' heading</t>
         </is>
       </c>
+      <c r="P162" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="62" t="n"/>
@@ -9313,6 +9797,9 @@
         <is>
           <t>1. Click anywhere on the page outside the dropdown</t>
         </is>
+      </c>
+      <c r="P163" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -9375,6 +9862,9 @@
           <t>1. Observe the Profile Image section</t>
         </is>
       </c>
+      <c r="P164" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="62" t="n"/>
@@ -9432,6 +9922,9 @@
           <t>1. Click the 'Upload an file' link in the Profile Image section</t>
         </is>
       </c>
+      <c r="P165" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="62" t="n"/>
@@ -9492,6 +9985,9 @@
  3. Click 'Open'</t>
         </is>
       </c>
+      <c r="P166" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="62" t="n"/>
@@ -9551,6 +10047,9 @@
  2. Click 'Open'</t>
         </is>
       </c>
+      <c r="P167" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="62" t="n"/>
@@ -9610,6 +10109,9 @@
  3. Click 'Open'</t>
         </is>
       </c>
+      <c r="P168" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="62" t="n"/>
@@ -9669,6 +10171,9 @@
  2. Drop it onto the dashed upload area</t>
         </is>
       </c>
+      <c r="P169" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="62" t="n"/>
@@ -9727,6 +10232,9 @@
  2. Drop it</t>
         </is>
       </c>
+      <c r="P170" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="62" t="n"/>
@@ -9785,6 +10293,9 @@
           <t>1. Click the bin/delete icon on the profile image</t>
         </is>
       </c>
+      <c r="P171" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="62" t="n"/>
@@ -9843,6 +10354,9 @@
  2. Click 'Update' button</t>
         </is>
       </c>
+      <c r="P172" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="62" t="n"/>
@@ -9902,6 +10416,9 @@
  3. Return to Profile page</t>
         </is>
       </c>
+      <c r="P173" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="62" t="n"/>
@@ -9959,6 +10476,9 @@
           <t>1. Attempt to upload an oversized PNG or JPG file</t>
         </is>
       </c>
+      <c r="P174" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="62" t="n"/>
@@ -10018,6 +10538,9 @@
  3. Click 'Update'</t>
         </is>
       </c>
+      <c r="P175" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="62" t="n"/>
@@ -10077,6 +10600,9 @@
  2. Observe the Name field</t>
         </is>
       </c>
+      <c r="P176" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="62" t="n"/>
@@ -10136,6 +10662,9 @@
  3. Type a new name (e.g., 'Test User')</t>
         </is>
       </c>
+      <c r="P177" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="62" t="n"/>
@@ -10194,6 +10723,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P178" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="62" t="n"/>
@@ -10252,6 +10784,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P179" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="62" t="n"/>
@@ -10309,6 +10844,9 @@
           <t>1. Observe the Name field label</t>
         </is>
       </c>
+      <c r="P180" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="62" t="n"/>
@@ -10368,6 +10906,9 @@
  3. Click 'Update'</t>
         </is>
       </c>
+      <c r="P181" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="62" t="n"/>
@@ -10426,6 +10967,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P182" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="62" t="n"/>
@@ -10484,6 +11028,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P183" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="62" t="n"/>
@@ -10542,6 +11089,9 @@
  2. Observe the Name field</t>
         </is>
       </c>
+      <c r="P184" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="62" t="n"/>
@@ -10600,6 +11150,9 @@
  2. Try to click on the Email field and type</t>
         </is>
       </c>
+      <c r="P185" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="62" t="n"/>
@@ -10657,6 +11210,9 @@
           <t>1. Observe Email field visually</t>
         </is>
       </c>
+      <c r="P186" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="62" t="n"/>
@@ -10716,6 +11272,9 @@
  2. Try to click and change the value</t>
         </is>
       </c>
+      <c r="P187" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="62" t="n"/>
@@ -10774,6 +11333,9 @@
  2. Navigate to Profile page</t>
         </is>
       </c>
+      <c r="P188" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="62" t="n"/>
@@ -10834,6 +11396,9 @@
  4. Click Update</t>
         </is>
       </c>
+      <c r="P189" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="62" t="n"/>
@@ -10893,6 +11458,9 @@
  3. Type new bank info (e.g., 'HDFC - 1234567890')</t>
         </is>
       </c>
+      <c r="P190" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="62" t="n"/>
@@ -10951,6 +11519,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P191" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="62" t="n"/>
@@ -11009,6 +11580,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P192" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="62" t="n"/>
@@ -11067,6 +11641,9 @@
  2. Clear and enter new value (e.g., 'GSTIN-27ABCDE1234F1Z5')</t>
         </is>
       </c>
+      <c r="P193" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="62" t="n"/>
@@ -11125,6 +11702,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P194" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="62" t="n"/>
@@ -11183,6 +11763,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P195" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="62" t="n"/>
@@ -11241,6 +11824,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P196" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="62" t="n"/>
@@ -11299,6 +11885,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P197" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="62" t="n"/>
@@ -11357,6 +11946,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P198" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="62" t="n"/>
@@ -11415,6 +12007,9 @@
  2. Observe the Update button</t>
         </is>
       </c>
+      <c r="P199" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="62" t="n"/>
@@ -11473,6 +12068,9 @@
           <t>1. Click 'Update' without changing any field</t>
         </is>
       </c>
+      <c r="P200" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="62" t="n"/>
@@ -11531,6 +12129,9 @@
  2. Click 'Update'</t>
         </is>
       </c>
+      <c r="P201" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="62" t="n"/>
@@ -11588,6 +12189,9 @@
           <t>1. Click the X icon on the success toast</t>
         </is>
       </c>
+      <c r="P202" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="62" t="n"/>
@@ -11646,6 +12250,9 @@
  2. Click Update</t>
         </is>
       </c>
+      <c r="P203" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="62" t="n"/>
@@ -11704,6 +12311,9 @@
  2. Immediately observe button state</t>
         </is>
       </c>
+      <c r="P204" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="62" t="n"/>
@@ -11764,6 +12374,9 @@
  3. Click 'Update'</t>
         </is>
       </c>
+      <c r="P205" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="62" t="n"/>
@@ -11822,6 +12435,9 @@
  2. Observe the dropdown</t>
         </is>
       </c>
+      <c r="P206" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="62" t="n"/>
@@ -11879,6 +12495,9 @@
           <t>1. Click 'Sign Out'</t>
         </is>
       </c>
+      <c r="P207" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="62" t="n"/>
@@ -11937,6 +12556,9 @@
  2. Attempt to navigate to a protected page</t>
         </is>
       </c>
+      <c r="P208" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="62" t="n"/>
@@ -11995,6 +12617,9 @@
  2. Press Enter</t>
         </is>
       </c>
+      <c r="P209" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="62" t="n"/>
@@ -12053,6 +12678,9 @@
  2. Check for session tokens for visdum.com</t>
         </is>
       </c>
+      <c r="P210" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="62" t="n"/>
@@ -12111,6 +12739,9 @@
  2. Click 'Sign Out' from Profile page</t>
         </is>
       </c>
+      <c r="P211" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="62" t="n"/>
@@ -12168,6 +12799,9 @@
           <t>1. Observe the page after redirect</t>
         </is>
       </c>
+      <c r="P212" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="62" t="n"/>
@@ -12227,6 +12861,9 @@
  2. Click 'Log In'</t>
         </is>
       </c>
+      <c r="P213" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="62" t="n"/>
@@ -12285,6 +12922,9 @@
  2. Check User B's session</t>
         </is>
       </c>
+      <c r="P214" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="62" t="n"/>
@@ -12343,6 +12983,9 @@
  2. Observe layout</t>
         </is>
       </c>
+      <c r="P215" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="62" t="n"/>
@@ -12401,6 +13044,9 @@
  2. Observe layout</t>
         </is>
       </c>
+      <c r="P216" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="62" t="n"/>
@@ -12459,6 +13105,9 @@
  2. Press Tab repeatedly</t>
         </is>
       </c>
+      <c r="P217" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="62" t="n"/>
@@ -12516,6 +13165,9 @@
           <t>1. Observe the browser tab title</t>
         </is>
       </c>
+      <c r="P218" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="62" t="n"/>
@@ -12575,6 +13227,9 @@
  3. Refresh in Tab 1</t>
         </is>
       </c>
+      <c r="P219" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="62" t="n"/>
@@ -12633,6 +13288,9 @@
  2. Press F5 (Refresh) before clicking Update</t>
         </is>
       </c>
+      <c r="P220" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="62" t="n"/>
@@ -12691,6 +13349,9 @@
  2. Click 'My Profile'</t>
         </is>
       </c>
+      <c r="P221" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="62" t="n"/>
@@ -12748,6 +13409,9 @@
           <t>1. Upload the corrupted PNG file</t>
         </is>
       </c>
+      <c r="P222" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="62" t="n"/>
@@ -12808,6 +13472,9 @@
  4. Try accessing User A's profile URL</t>
         </is>
       </c>
+      <c r="P223" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="62" t="n"/>
@@ -12865,6 +13532,9 @@
           <t>1. Enter a script tag in Name: &lt;script&gt;alert('XSS')&lt;/script&gt;
  2. Click Update</t>
         </is>
+      </c>
+      <c r="P224" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -12940,6 +13610,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P226" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="59" t="n"/>
@@ -12995,6 +13668,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P227" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="59" t="n"/>
@@ -13050,6 +13726,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P228" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="59" t="n"/>
@@ -13105,6 +13784,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P229" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="59" t="n"/>
@@ -13160,6 +13842,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P230" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="59" t="n"/>
@@ -13215,6 +13900,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P231" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="59" t="n"/>
@@ -13270,6 +13958,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P232" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="59" t="n"/>
@@ -13325,6 +14016,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P233" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="59" t="n"/>
@@ -13380,6 +14074,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P234" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="59" t="n"/>
@@ -13435,6 +14132,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P235" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="59" t="n"/>
@@ -13490,6 +14190,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P236" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="59" t="n"/>
@@ -13545,6 +14248,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P237" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="59" t="n"/>
@@ -13600,6 +14306,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P238" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="59" t="n"/>
@@ -13655,6 +14364,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P239" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="59" t="n"/>
@@ -13709,6 +14421,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P240" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -13732,7 +14447,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O221"/>
+  <dimension ref="A1:P221"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -13851,6 +14566,9 @@
           <t>Test Steps</t>
         </is>
       </c>
+      <c r="P3" t="s" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -13907,6 +14625,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P4" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -13957,6 +14678,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P5" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -14006,6 +14730,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P6" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -14055,6 +14782,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P7" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -14104,6 +14834,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P8" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -14153,6 +14886,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P9" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -14202,6 +14938,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P10" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -14251,6 +14990,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P11" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -14300,6 +15042,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P12" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -14349,6 +15094,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P13" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -14398,6 +15146,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P14" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -14447,6 +15198,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P15" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -14496,6 +15250,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P16" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -14545,6 +15302,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P17" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -14594,6 +15354,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P18" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -14643,6 +15406,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P19" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -14692,6 +15458,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P20" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -14741,6 +15510,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P21" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -14790,6 +15562,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P22" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -14839,6 +15614,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P23" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -14888,6 +15666,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P24" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -14937,6 +15718,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P25" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -14986,6 +15770,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P26" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -15034,6 +15821,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P27" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -15109,6 +15899,9 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="P29" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -15169,6 +15962,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P30" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -15229,6 +16025,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P31" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -15289,6 +16088,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P32" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -15349,6 +16151,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P33" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -15409,6 +16214,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P34" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -15469,6 +16277,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P35" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -15529,6 +16340,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P36" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -15589,6 +16403,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P37" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -15649,6 +16466,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P38" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -15709,6 +16529,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P39" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -15769,6 +16592,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P40" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -15828,6 +16654,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P41" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -15890,6 +16719,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P42" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -15951,6 +16783,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P43" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
@@ -16012,6 +16847,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P44" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -16073,6 +16911,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P45" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -16134,6 +16975,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P46" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -16193,6 +17037,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P47" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -16255,6 +17102,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P48" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
@@ -16315,6 +17165,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P49" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
@@ -16375,6 +17228,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P50" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
@@ -16435,6 +17291,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P51" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
@@ -16495,6 +17354,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P52" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
@@ -16555,6 +17417,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P53" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
@@ -16615,6 +17480,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P54" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -16675,6 +17543,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P55" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
@@ -16735,6 +17606,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P56" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
@@ -16795,6 +17669,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P57" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
@@ -16855,6 +17732,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P58" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
@@ -16915,6 +17795,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P59" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -16975,6 +17858,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P60" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
@@ -17034,6 +17920,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P61" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
@@ -17093,6 +17982,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P62" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
@@ -17153,6 +18045,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P63" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -17212,6 +18107,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P64" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
@@ -17272,6 +18170,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P65" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
@@ -17331,6 +18232,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P66" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -17394,6 +18298,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P67" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
@@ -17456,6 +18363,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P68" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
@@ -17518,6 +18428,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P69" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
@@ -17580,6 +18493,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P70" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
@@ -17640,6 +18556,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P71" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
@@ -17699,6 +18618,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P72" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -17761,6 +18683,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P73" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
@@ -17820,6 +18745,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P74" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -17883,6 +18811,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P75" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
@@ -17943,6 +18874,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P76" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
@@ -18002,6 +18936,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P77" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
@@ -18062,6 +18999,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P78" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
@@ -18122,6 +19062,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P79" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
@@ -18182,6 +19125,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P80" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
@@ -18242,6 +19188,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P81" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
@@ -18302,6 +19251,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P82" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
@@ -18362,6 +19314,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P83" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
@@ -18421,6 +19376,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P84" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -18474,6 +19432,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P85" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
@@ -18526,6 +19487,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P86" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
@@ -18578,6 +19542,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P87" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
@@ -18630,6 +19597,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P88" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
@@ -18682,6 +19652,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P89" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
@@ -18734,6 +19707,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P90" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
@@ -18786,6 +19762,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P91" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
@@ -18838,6 +19817,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P92" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
@@ -18890,6 +19872,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P93" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
@@ -18942,6 +19927,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P94" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
@@ -18994,6 +19982,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P95" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
@@ -19054,6 +20045,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P96" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="inlineStr">
@@ -19113,6 +20107,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P97" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -19175,6 +20172,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P98" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
@@ -19236,6 +20236,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P99" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
@@ -19296,6 +20299,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P100" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="inlineStr">
@@ -19356,6 +20362,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P101" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
@@ -19416,6 +20425,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P102" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="inlineStr">
@@ -19475,6 +20487,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P103" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
@@ -19534,6 +20549,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P104" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -19596,6 +20614,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P105" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
@@ -19656,6 +20677,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P106" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="inlineStr">
@@ -19716,6 +20740,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P107" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
@@ -19775,6 +20802,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P108" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
@@ -19835,6 +20865,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P109" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
@@ -19895,6 +20928,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P110" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
@@ -19955,6 +20991,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P111" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
@@ -20015,6 +21054,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P112" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
@@ -20074,6 +21116,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P113" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
@@ -20133,6 +21178,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P114" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
@@ -20192,6 +21240,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P115" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
@@ -20251,6 +21302,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P116" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
@@ -20311,6 +21365,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P117" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
@@ -20371,6 +21428,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P118" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
@@ -20431,6 +21491,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P119" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
@@ -20491,6 +21554,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P120" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
@@ -20551,6 +21617,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P121" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
@@ -20611,6 +21680,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P122" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
@@ -20671,6 +21743,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P123" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
@@ -20730,6 +21805,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P124" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -20792,6 +21870,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P125" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
@@ -20851,6 +21932,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P126" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="inlineStr">
@@ -20911,6 +21995,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P127" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
@@ -20971,6 +22058,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P128" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="inlineStr">
@@ -21031,6 +22121,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P129" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
@@ -21091,6 +22184,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P130" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="14" t="inlineStr">
@@ -21151,6 +22247,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P131" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
@@ -21211,6 +22310,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P132" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
@@ -21270,6 +22372,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P133" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
@@ -21329,6 +22434,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P134" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -21391,6 +22499,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P135" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
@@ -21450,6 +22561,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P136" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
@@ -21510,6 +22624,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P137" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
@@ -21569,6 +22686,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P138" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
@@ -21629,6 +22749,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P139" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
@@ -21689,6 +22812,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P140" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="14" t="inlineStr">
@@ -21748,6 +22874,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P141" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
@@ -21807,6 +22936,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P142" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="14" t="inlineStr">
@@ -21866,6 +22998,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P143" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
@@ -21924,6 +23059,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P144" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -21986,6 +23124,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P145" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
@@ -22045,6 +23186,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P146" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="14" t="inlineStr">
@@ -22104,6 +23248,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P147" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
@@ -22163,6 +23310,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P148" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="14" t="inlineStr">
@@ -22222,6 +23372,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P149" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
@@ -22281,6 +23434,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P150" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="14" t="inlineStr">
@@ -22341,6 +23497,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P151" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
@@ -22400,6 +23559,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P152" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="14" t="inlineStr">
@@ -22459,6 +23621,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P153" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
@@ -22519,6 +23684,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P154" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="14" t="inlineStr">
@@ -22578,6 +23746,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P155" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
@@ -22637,6 +23808,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P156" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="14" t="inlineStr">
@@ -22697,6 +23871,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P157" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
@@ -22757,6 +23934,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P158" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="14" t="inlineStr">
@@ -22816,6 +23996,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P159" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
@@ -22875,6 +24058,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P160" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="14" t="inlineStr">
@@ -22935,6 +24121,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P161" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
@@ -22994,6 +24183,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P162" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="14" t="inlineStr">
@@ -23054,6 +24246,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P163" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
@@ -23114,6 +24309,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P164" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="14" t="inlineStr">
@@ -23174,6 +24372,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P165" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
@@ -23234,6 +24435,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P166" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="14" t="inlineStr">
@@ -23294,6 +24498,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P167" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
@@ -23354,6 +24561,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P168" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="14" t="inlineStr">
@@ -23414,6 +24624,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P169" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
@@ -23473,6 +24686,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P170" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -23534,6 +24750,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P171" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -23599,6 +24818,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P172" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="14" t="inlineStr">
@@ -23660,6 +24882,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P173" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
@@ -23719,6 +24944,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P174" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="14" t="inlineStr">
@@ -23778,6 +25006,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P175" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -23840,6 +25071,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P176" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="14" t="inlineStr">
@@ -23900,6 +25134,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P177" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
@@ -23960,6 +25197,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P178" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="14" t="inlineStr">
@@ -24020,6 +25260,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P179" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
@@ -24080,6 +25323,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P180" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="14" t="inlineStr">
@@ -24140,6 +25386,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P181" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
@@ -24200,6 +25449,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P182" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="14" t="inlineStr">
@@ -24260,6 +25512,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P183" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
@@ -24319,6 +25574,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P184" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="14" t="inlineStr">
@@ -24378,6 +25636,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P185" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
@@ -24438,6 +25699,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P186" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="14" t="inlineStr">
@@ -24497,6 +25761,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P187" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
@@ -24557,6 +25824,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P188" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="14" t="inlineStr">
@@ -24615,6 +25885,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P189" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -24678,6 +25951,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P190" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="14" t="inlineStr">
@@ -24738,6 +26014,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P191" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
@@ -24798,6 +26077,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P192" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="inlineStr">
@@ -24857,6 +26139,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P193" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="inlineStr">
@@ -24916,6 +26201,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P194" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="14" t="inlineStr">
@@ -24975,6 +26263,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P195" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -25037,6 +26328,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P196" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="14" t="inlineStr">
@@ -25095,6 +26389,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P197" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -25163,6 +26460,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P198" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="14" t="inlineStr">
@@ -25226,6 +26526,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P199" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="14" t="inlineStr">
@@ -25285,6 +26588,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P200" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -25346,6 +26652,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P201" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -25409,6 +26718,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P202" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="14" t="inlineStr">
@@ -25470,6 +26782,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P203" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -25536,6 +26851,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P204" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="14" t="inlineStr">
@@ -25596,6 +26914,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P205" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -25671,6 +26992,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P207" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="59" t="n"/>
@@ -25725,6 +27049,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P208" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -25777,6 +27104,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P209" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="59" t="n"/>
@@ -25831,6 +27161,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P210" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -25883,6 +27216,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P211" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="59" t="n"/>
@@ -25937,6 +27273,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P212" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="213">
@@ -25989,6 +27328,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P213" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="59" t="n"/>
@@ -26040,6 +27382,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P214" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="59" t="n"/>
@@ -26095,6 +27440,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P215" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="59" t="n"/>
@@ -26150,6 +27498,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P216" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="59" t="n"/>
@@ -26205,6 +27556,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P217" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="59" t="n"/>
@@ -26260,6 +27614,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P218" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="59" t="n"/>
@@ -26315,6 +27672,9 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="P219" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="59" t="n"/>
@@ -26370,6 +27730,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P220" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="59" t="n"/>
@@ -26424,6 +27787,9 @@
         <is>
           <t>Minor</t>
         </is>
+      </c>
+      <c r="P221" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -26538,6 +27904,9 @@
           <t>Test Steps</t>
         </is>
       </c>
+      <c r="P2" t="s" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -26588,6 +27957,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P3" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -26638,6 +28010,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P4" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -26688,6 +28063,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P5" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -26738,6 +28116,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P6" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -26788,6 +28169,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P7" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -26838,6 +28222,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P8" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -26888,6 +28275,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P9" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -26938,6 +28328,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P10" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -26988,6 +28381,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P11" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -27038,6 +28434,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P12" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -27088,6 +28487,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P13" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -27138,6 +28540,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P14" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -27188,6 +28593,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P15" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -27238,6 +28646,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P16" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -27288,6 +28699,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P17" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -27338,6 +28752,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P18" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -27388,6 +28805,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P19" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -27438,6 +28858,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P20" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -27488,6 +28911,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P21" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -27538,6 +28964,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P22" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -27588,6 +29017,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P23" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -27638,6 +29070,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P24" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -27688,6 +29123,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P25" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -27738,6 +29176,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P26" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -27788,6 +29229,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P27" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -27838,6 +29282,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P28" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -27888,6 +29335,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P29" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -27938,6 +29388,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P30" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -27988,6 +29441,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P31" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -28038,6 +29494,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P32" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -28088,6 +29547,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P33" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -28138,6 +29600,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P34" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -28188,6 +29653,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P35" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -28238,6 +29706,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P36" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -28288,6 +29759,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P37" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -28338,6 +29812,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P38" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -28388,6 +29865,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P39" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -28438,6 +29918,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P40" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -28488,6 +29971,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P41" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -28538,6 +30024,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P42" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -28588,6 +30077,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P43" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -28638,6 +30130,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P44" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -28688,6 +30183,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P45" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -28738,6 +30236,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P46" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -28788,6 +30289,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P47" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -28838,6 +30342,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P48" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -28888,6 +30395,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P49" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -28938,6 +30448,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P50" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -28988,6 +30501,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P51" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -29038,6 +30554,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P52" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -29097,7 +30616,9 @@
       <c r="M53" s="5" t="n"/>
       <c r="N53" s="5" t="n"/>
       <c r="O53" s="5" t="n"/>
-      <c r="P53" s="5" t="n"/>
+      <c r="P53" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q53" s="5" t="n"/>
       <c r="R53" s="5" t="n"/>
       <c r="S53" s="5" t="n"/>
@@ -29159,7 +30680,9 @@
       <c r="M54" s="5" t="n"/>
       <c r="N54" s="5" t="n"/>
       <c r="O54" s="5" t="n"/>
-      <c r="P54" s="5" t="n"/>
+      <c r="P54" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q54" s="5" t="n"/>
       <c r="R54" s="5" t="n"/>
       <c r="S54" s="5" t="n"/>
@@ -29225,7 +30748,9 @@
       </c>
       <c r="N55" s="5" t="n"/>
       <c r="O55" s="5" t="n"/>
-      <c r="P55" s="5" t="n"/>
+      <c r="P55" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q55" s="5" t="n"/>
       <c r="R55" s="5" t="n"/>
       <c r="S55" s="5" t="n"/>
@@ -29287,7 +30812,9 @@
       <c r="M56" s="5" t="n"/>
       <c r="N56" s="5" t="n"/>
       <c r="O56" s="5" t="n"/>
-      <c r="P56" s="5" t="n"/>
+      <c r="P56" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q56" s="5" t="n"/>
       <c r="R56" s="5" t="n"/>
       <c r="S56" s="5" t="n"/>
@@ -29349,7 +30876,9 @@
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="n"/>
       <c r="O57" s="5" t="n"/>
-      <c r="P57" s="5" t="n"/>
+      <c r="P57" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q57" s="5" t="n"/>
       <c r="R57" s="5" t="n"/>
       <c r="S57" s="5" t="n"/>
@@ -29415,7 +30944,9 @@
       </c>
       <c r="N58" s="5" t="n"/>
       <c r="O58" s="5" t="n"/>
-      <c r="P58" s="5" t="n"/>
+      <c r="P58" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q58" s="5" t="n"/>
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5" t="n"/>
@@ -29477,7 +31008,9 @@
       <c r="M59" s="5" t="n"/>
       <c r="N59" s="5" t="n"/>
       <c r="O59" s="5" t="n"/>
-      <c r="P59" s="5" t="n"/>
+      <c r="P59" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q59" s="5" t="n"/>
       <c r="R59" s="5" t="n"/>
       <c r="S59" s="5" t="n"/>
@@ -29539,7 +31072,9 @@
       <c r="M60" s="5" t="n"/>
       <c r="N60" s="5" t="n"/>
       <c r="O60" s="5" t="n"/>
-      <c r="P60" s="5" t="n"/>
+      <c r="P60" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q60" s="5" t="n"/>
       <c r="R60" s="5" t="n"/>
       <c r="S60" s="5" t="n"/>
@@ -29601,7 +31136,9 @@
       <c r="M61" s="5" t="n"/>
       <c r="N61" s="5" t="n"/>
       <c r="O61" s="5" t="n"/>
-      <c r="P61" s="5" t="n"/>
+      <c r="P61" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q61" s="5" t="n"/>
       <c r="R61" s="5" t="n"/>
       <c r="S61" s="5" t="n"/>
@@ -29685,6 +31222,9 @@
           <t>GENUINE Team-specific Sort &amp; Filter coverage was missing — see summary re: rows 54-60/61-112 in this sheet appearing to be Department content, not Team content.</t>
         </is>
       </c>
+      <c r="P63" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="59" t="inlineStr">
@@ -29735,6 +31275,9 @@
         </is>
       </c>
       <c r="M64" s="59" t="n"/>
+      <c r="P64" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="59" t="inlineStr">
@@ -29785,6 +31328,9 @@
         </is>
       </c>
       <c r="M65" s="59" t="n"/>
+      <c r="P65" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="59" t="inlineStr">
@@ -29835,6 +31381,9 @@
         </is>
       </c>
       <c r="M66" s="59" t="n"/>
+      <c r="P66" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="59" t="inlineStr">
@@ -29885,6 +31434,9 @@
         </is>
       </c>
       <c r="M67" s="59" t="n"/>
+      <c r="P67" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="59" t="inlineStr">
@@ -29935,6 +31487,9 @@
         </is>
       </c>
       <c r="M68" s="59" t="n"/>
+      <c r="P68" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="59" t="inlineStr">
@@ -29989,6 +31544,9 @@
           <t>Confirmed via code review: filterParams has no buttons configured.</t>
         </is>
       </c>
+      <c r="P69" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="59" t="inlineStr">
@@ -30039,6 +31597,9 @@
         </is>
       </c>
       <c r="M70" s="59" t="n"/>
+      <c r="P70" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="59" t="inlineStr">
@@ -30089,6 +31650,9 @@
         </is>
       </c>
       <c r="M71" s="59" t="n"/>
+      <c r="P71" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="59" t="inlineStr">
@@ -30143,6 +31707,9 @@
           <t>Existing legacy case TS_12_TC_03 claims alphanumeric-only is enforced; current TeamForm.tsx validation schema (Yup) only enforces required + min 3 + max 50, with no alphanumeric-only rule. Recommend the QA team verify current behavior against the legacy assumption.</t>
         </is>
       </c>
+      <c r="P72" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="59" t="inlineStr">
@@ -30193,6 +31760,9 @@
         </is>
       </c>
       <c r="M73" s="59" t="n"/>
+      <c r="P73" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="59" t="inlineStr">
@@ -30243,6 +31813,9 @@
         </is>
       </c>
       <c r="M74" s="59" t="n"/>
+      <c r="P74" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="59" t="inlineStr">
@@ -30297,6 +31870,9 @@
           <t>Existing legacy case TS_12_TC_06 claims a 2000-character limit is enforced; current TeamForm.tsx has the description validation commented out (notRequired only). Recommend the QA team verify against the legacy assumption.</t>
         </is>
       </c>
+      <c r="P75" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="59" t="inlineStr">
@@ -30347,6 +31923,9 @@
         </is>
       </c>
       <c r="M76" s="59" t="n"/>
+      <c r="P76" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="59" t="inlineStr">
@@ -30397,6 +31976,9 @@
         </is>
       </c>
       <c r="M77" s="59" t="n"/>
+      <c r="P77" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="59" t="inlineStr">
@@ -30447,6 +32029,9 @@
         </is>
       </c>
       <c r="M78" s="59" t="n"/>
+      <c r="P78" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30560,6 +32145,9 @@
           <t>Test Steps</t>
         </is>
       </c>
+      <c r="P2" t="s" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -30616,6 +32204,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P3" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="n"/>
@@ -30666,6 +32257,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P4" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="n"/>
@@ -30716,6 +32310,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P5" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="n"/>
@@ -30766,6 +32363,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P6" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n"/>
@@ -30816,6 +32416,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P7" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
@@ -30866,6 +32469,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P8" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n"/>
@@ -30916,6 +32522,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P9" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="n"/>
@@ -30966,6 +32575,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P10" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n"/>
@@ -31016,6 +32628,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P11" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
@@ -31066,6 +32681,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P12" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n"/>
@@ -31116,6 +32734,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P13" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n"/>
@@ -31166,6 +32787,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P14" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n"/>
@@ -31216,6 +32840,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P15" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n"/>
@@ -31266,6 +32893,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P16" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="n"/>
@@ -31316,6 +32946,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P17" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="n"/>
@@ -31366,6 +32999,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P18" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="n"/>
@@ -31416,6 +33052,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P19" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n"/>
@@ -31466,6 +33105,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P20" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="n"/>
@@ -31516,6 +33158,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P21" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="n"/>
@@ -31566,6 +33211,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P22" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="n"/>
@@ -31616,6 +33264,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P23" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="n"/>
@@ -31666,6 +33317,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P24" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n"/>
@@ -31716,6 +33370,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P25" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="n"/>
@@ -31766,6 +33423,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P26" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="n"/>
@@ -31816,6 +33476,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P27" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n"/>
@@ -31866,6 +33529,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P28" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n"/>
@@ -31916,6 +33582,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P29" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n"/>
@@ -31966,6 +33635,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P30" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n"/>
@@ -32016,6 +33688,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P31" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n"/>
@@ -32066,6 +33741,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P32" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="n"/>
@@ -32116,6 +33794,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P33" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n"/>
@@ -32166,6 +33847,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P34" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="n"/>
@@ -32216,6 +33900,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P35" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="n"/>
@@ -32266,6 +33953,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P36" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="n"/>
@@ -32316,6 +34006,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P37" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="n"/>
@@ -32366,6 +34059,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P38" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="n"/>
@@ -32416,6 +34112,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P39" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="n"/>
@@ -32466,6 +34165,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P40" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="n"/>
@@ -32516,6 +34218,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P41" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="n"/>
@@ -32566,6 +34271,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P42" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="n"/>
@@ -32616,6 +34324,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P43" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="n"/>
@@ -32666,6 +34377,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P44" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="n"/>
@@ -32716,6 +34430,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P45" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="n"/>
@@ -32766,6 +34483,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P46" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="n"/>
@@ -32816,6 +34536,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P47" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="n"/>
@@ -32866,6 +34589,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P48" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="n"/>
@@ -32916,6 +34642,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P49" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="n"/>
@@ -32966,6 +34695,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P50" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n"/>
@@ -33016,6 +34748,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P51" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n"/>
@@ -33066,6 +34801,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P52" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n"/>
@@ -33116,6 +34854,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P53" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n"/>
@@ -33166,6 +34907,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P54" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n"/>
@@ -33216,6 +34960,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P55" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="n"/>
@@ -33266,6 +35013,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P56" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="15" t="n"/>
@@ -33316,6 +35066,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P57" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="15" t="n"/>
@@ -33366,6 +35119,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P58" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="15" t="n"/>
@@ -33416,6 +35172,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P59" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="15" t="n"/>
@@ -33466,6 +35225,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P60" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="15" t="n"/>
@@ -33516,6 +35278,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P61" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="15" t="n"/>
@@ -33566,6 +35331,9 @@
           <t>Minor</t>
         </is>
       </c>
+      <c r="P62" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="15" t="n"/>
@@ -33616,6 +35384,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P63" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="15" t="n"/>
@@ -33666,6 +35437,9 @@
           <t>Major</t>
         </is>
       </c>
+      <c r="P64" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="15" t="n"/>
@@ -33715,6 +35489,9 @@
         <is>
           <t>Major</t>
         </is>
+      </c>
+      <c r="P65" t="s" s="0">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -33843,7 +35620,9 @@
       <c r="M67" s="5" t="n"/>
       <c r="N67" s="5" t="n"/>
       <c r="O67" s="5" t="n"/>
-      <c r="P67" s="5" t="n"/>
+      <c r="P67" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q67" s="5" t="n"/>
       <c r="R67" s="5" t="n"/>
       <c r="S67" s="5" t="n"/>
@@ -33905,7 +35684,9 @@
       <c r="M68" s="5" t="n"/>
       <c r="N68" s="5" t="n"/>
       <c r="O68" s="5" t="n"/>
-      <c r="P68" s="5" t="n"/>
+      <c r="P68" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q68" s="5" t="n"/>
       <c r="R68" s="5" t="n"/>
       <c r="S68" s="5" t="n"/>
@@ -33967,7 +35748,9 @@
       <c r="M69" s="5" t="n"/>
       <c r="N69" s="5" t="n"/>
       <c r="O69" s="5" t="n"/>
-      <c r="P69" s="5" t="n"/>
+      <c r="P69" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q69" s="5" t="n"/>
       <c r="R69" s="5" t="n"/>
       <c r="S69" s="5" t="n"/>
@@ -34029,7 +35812,9 @@
       <c r="M70" s="5" t="n"/>
       <c r="N70" s="5" t="n"/>
       <c r="O70" s="5" t="n"/>
-      <c r="P70" s="5" t="n"/>
+      <c r="P70" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q70" s="5" t="n"/>
       <c r="R70" s="5" t="n"/>
       <c r="S70" s="5" t="n"/>
@@ -34091,7 +35876,9 @@
       <c r="M71" s="5" t="n"/>
       <c r="N71" s="5" t="n"/>
       <c r="O71" s="5" t="n"/>
-      <c r="P71" s="5" t="n"/>
+      <c r="P71" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q71" s="5" t="n"/>
       <c r="R71" s="5" t="n"/>
       <c r="S71" s="5" t="n"/>
@@ -34153,7 +35940,9 @@
       <c r="M72" s="5" t="n"/>
       <c r="N72" s="5" t="n"/>
       <c r="O72" s="5" t="n"/>
-      <c r="P72" s="5" t="n"/>
+      <c r="P72" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q72" s="5" t="n"/>
       <c r="R72" s="5" t="n"/>
       <c r="S72" s="5" t="n"/>
@@ -34215,7 +36004,9 @@
       <c r="M73" s="5" t="n"/>
       <c r="N73" s="5" t="n"/>
       <c r="O73" s="5" t="n"/>
-      <c r="P73" s="5" t="n"/>
+      <c r="P73" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q73" s="5" t="n"/>
       <c r="R73" s="5" t="n"/>
       <c r="S73" s="5" t="n"/>
@@ -34277,7 +36068,9 @@
       <c r="M74" s="5" t="n"/>
       <c r="N74" s="5" t="n"/>
       <c r="O74" s="5" t="n"/>
-      <c r="P74" s="5" t="n"/>
+      <c r="P74" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q74" s="5" t="n"/>
       <c r="R74" s="5" t="n"/>
       <c r="S74" s="5" t="n"/>
@@ -34339,7 +36132,9 @@
       <c r="M75" s="5" t="n"/>
       <c r="N75" s="5" t="n"/>
       <c r="O75" s="5" t="n"/>
-      <c r="P75" s="5" t="n"/>
+      <c r="P75" s="0" t="s">
+        <v>2</v>
+      </c>
       <c r="Q75" s="5" t="n"/>
       <c r="R75" s="5" t="n"/>
       <c r="S75" s="5" t="n"/>
@@ -34419,6 +36214,9 @@
         </is>
       </c>
       <c r="M77" s="59" t="n"/>
+      <c r="P77" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="59" t="inlineStr">
@@ -34469,6 +36267,9 @@
         </is>
       </c>
       <c r="M78" s="59" t="n"/>
+      <c r="P78" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="59" t="inlineStr">
@@ -34519,6 +36320,9 @@
         </is>
       </c>
       <c r="M79" s="59" t="n"/>
+      <c r="P79" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="59" t="inlineStr">
@@ -34569,6 +36373,9 @@
         </is>
       </c>
       <c r="M80" s="59" t="n"/>
+      <c r="P80" t="s" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="59" t="inlineStr">
@@ -34619,6 +36426,9 @@
         </is>
       </c>
       <c r="M81" s="59" t="n"/>
+      <c r="P81" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="59" t="inlineStr">
@@ -34669,6 +36479,9 @@
         </is>
       </c>
       <c r="M82" s="59" t="n"/>
+      <c r="P82" t="s" s="0">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/test/resources/manual-testcases.xlsx
+++ b/src/test/resources/manual-testcases.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Team" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Departments" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Resources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Refresh Columns" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -104,8 +105,23 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -147,8 +163,14 @@
         <bgColor rgb="00E9ECEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -239,11 +261,25 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -433,6 +469,16 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -856,6 +902,11 @@
       <c r="I4" s="11" t="n"/>
       <c r="J4" s="13" t="n"/>
       <c r="K4" s="11" t="n"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -915,7 +966,7 @@
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -977,7 +1028,7 @@
       </c>
       <c r="P6" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1090,7 @@
       </c>
       <c r="P7" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1152,7 @@
       </c>
       <c r="P8" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1214,7 @@
       </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1276,7 @@
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1338,7 @@
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1400,7 @@
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1462,7 @@
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1524,7 @@
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1586,7 @@
       </c>
       <c r="P15" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1772,7 @@
       </c>
       <c r="P18" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4135,6 +4186,11 @@
       <c r="I57" s="11" t="n"/>
       <c r="J57" s="13" t="n"/>
       <c r="K57" s="11" t="n"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="20" t="n"/>
@@ -5186,7 +5242,7 @@
       </c>
       <c r="P74" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6360,7 @@
       </c>
       <c r="P92" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7890,7 @@
       </c>
       <c r="P120" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7942,7 @@
       </c>
       <c r="P121" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7994,7 @@
       </c>
       <c r="P122" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7990,7 +8046,7 @@
       </c>
       <c r="P123" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8098,7 @@
       </c>
       <c r="P124" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8150,7 @@
       </c>
       <c r="P125" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8358,7 @@
       </c>
       <c r="P129" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8634,6 +8690,11 @@
       <c r="I136" s="11" t="n"/>
       <c r="J136" s="13" t="n"/>
       <c r="K136" s="11" t="n"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -8799,7 +8860,7 @@
       </c>
       <c r="P139" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8855,7 +8916,7 @@
       </c>
       <c r="P140" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8972,7 @@
       </c>
       <c r="P141" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9364,7 @@
       </c>
       <c r="P148" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9771,6 +9832,11 @@
       <c r="I157" s="27" t="n"/>
       <c r="J157" s="27" t="n"/>
       <c r="K157" s="27" t="n"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="62" t="n"/>
@@ -14025,6 +14091,11 @@
       <c r="K225" s="58" t="n"/>
       <c r="L225" s="58" t="n"/>
       <c r="M225" s="58" t="n"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="59" t="n"/>
@@ -16392,6 +16463,11 @@
       <c r="I28" s="27" t="n"/>
       <c r="J28" s="29" t="n"/>
       <c r="K28" s="27" t="n"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="30" t="inlineStr">
@@ -16776,7 +16852,7 @@
       </c>
       <c r="P34" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16917,7 @@
       </c>
       <c r="P35" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16971,7 +17047,7 @@
       </c>
       <c r="P37" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17177,7 @@
       </c>
       <c r="P39" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17231,7 +17307,7 @@
       </c>
       <c r="P41" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17297,7 +17373,7 @@
       </c>
       <c r="P42" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17363,7 +17439,7 @@
       </c>
       <c r="P43" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17429,7 +17505,7 @@
       </c>
       <c r="P44" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17495,7 +17571,7 @@
       </c>
       <c r="P45" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17561,7 +17637,7 @@
       </c>
       <c r="P46" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17626,7 +17702,7 @@
       </c>
       <c r="P47" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17692,7 +17768,7 @@
       </c>
       <c r="P48" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17833,7 @@
       </c>
       <c r="P49" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17898,7 @@
       </c>
       <c r="P50" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17887,7 +17963,7 @@
       </c>
       <c r="P51" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -17952,7 +18028,7 @@
       </c>
       <c r="P52" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18017,7 +18093,7 @@
       </c>
       <c r="P53" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18082,7 +18158,7 @@
       </c>
       <c r="P54" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18147,7 +18223,7 @@
       </c>
       <c r="P55" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18212,7 +18288,7 @@
       </c>
       <c r="P56" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18277,7 +18353,7 @@
       </c>
       <c r="P57" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18342,7 +18418,7 @@
       </c>
       <c r="P58" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18407,7 +18483,7 @@
       </c>
       <c r="P59" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18548,7 @@
       </c>
       <c r="P60" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18870,7 @@
       </c>
       <c r="P65" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18859,7 +18935,7 @@
       </c>
       <c r="P66" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18926,7 +19002,7 @@
       </c>
       <c r="P67" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -18993,7 +19069,7 @@
       </c>
       <c r="P68" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19136,7 @@
       </c>
       <c r="P69" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19203,7 @@
       </c>
       <c r="P70" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19192,7 +19268,7 @@
       </c>
       <c r="P71" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19257,7 +19333,7 @@
       </c>
       <c r="P72" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19399,7 @@
       </c>
       <c r="P73" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19388,7 +19464,7 @@
       </c>
       <c r="P74" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19455,7 +19531,7 @@
       </c>
       <c r="P75" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -19520,7 +19596,7 @@
       </c>
       <c r="P76" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21707,7 +21783,7 @@
       </c>
       <c r="P111" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -21964,7 +22040,7 @@
       </c>
       <c r="P115" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23403,7 @@
       </c>
       <c r="P136" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -23908,7 +23984,7 @@
       </c>
       <c r="P145" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -24486,7 +24562,7 @@
       </c>
       <c r="P154" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27819,7 +27895,7 @@
       </c>
       <c r="P205" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27841,6 +27917,11 @@
       <c r="K206" s="58" t="n"/>
       <c r="L206" s="58" t="n"/>
       <c r="M206" s="58" t="n"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="59" t="n"/>
@@ -27898,7 +27979,7 @@
       </c>
       <c r="P207" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -27958,7 +28039,7 @@
       </c>
       <c r="P208" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28014,7 +28095,7 @@
       </c>
       <c r="P209" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28074,7 +28155,7 @@
       </c>
       <c r="P210" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28130,7 +28211,7 @@
       </c>
       <c r="P211" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28190,7 +28271,7 @@
       </c>
       <c r="P212" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28246,7 +28327,7 @@
       </c>
       <c r="P213" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28302,7 +28383,7 @@
       </c>
       <c r="P214" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28362,7 +28443,7 @@
       </c>
       <c r="P215" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28422,7 +28503,7 @@
       </c>
       <c r="P216" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28563,7 @@
       </c>
       <c r="P217" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29335,7 +29416,7 @@
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29445,7 +29526,7 @@
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29500,7 +29581,7 @@
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29555,7 +29636,7 @@
       </c>
       <c r="P15" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29610,7 +29691,7 @@
       </c>
       <c r="P16" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -29665,7 +29746,7 @@
       </c>
       <c r="P17" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30160,7 +30241,7 @@
       </c>
       <c r="P26" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30215,7 +30296,7 @@
       </c>
       <c r="P27" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30270,7 +30351,7 @@
       </c>
       <c r="P28" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30325,7 +30406,7 @@
       </c>
       <c r="P29" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30380,7 +30461,7 @@
       </c>
       <c r="P30" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30435,7 +30516,7 @@
       </c>
       <c r="P31" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32222,6 +32303,11 @@
       <c r="K62" s="58" t="n"/>
       <c r="L62" s="58" t="n"/>
       <c r="M62" s="58" t="n"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="59" t="inlineStr">
@@ -32498,7 +32584,7 @@
       <c r="M67" s="59" t="n"/>
       <c r="P67" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32553,7 +32639,7 @@
       <c r="M68" s="59" t="n"/>
       <c r="P68" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32612,7 +32698,7 @@
       </c>
       <c r="P69" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33734,7 +33820,7 @@
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33844,7 +33930,7 @@
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33899,7 +33985,7 @@
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -33954,7 +34040,7 @@
       </c>
       <c r="P15" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34009,7 +34095,7 @@
       </c>
       <c r="P16" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34064,7 +34150,7 @@
       </c>
       <c r="P17" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34119,7 +34205,7 @@
       </c>
       <c r="P18" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34174,7 +34260,7 @@
       </c>
       <c r="P19" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34229,7 +34315,7 @@
       </c>
       <c r="P20" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34284,7 +34370,7 @@
       </c>
       <c r="P21" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34339,7 +34425,7 @@
       </c>
       <c r="P22" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34394,7 +34480,7 @@
       </c>
       <c r="P23" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34449,7 +34535,7 @@
       </c>
       <c r="P24" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34504,7 +34590,7 @@
       </c>
       <c r="P25" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -34559,7 +34645,7 @@
       </c>
       <c r="P26" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35109,7 +35195,7 @@
       </c>
       <c r="P36" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35164,7 +35250,7 @@
       </c>
       <c r="P37" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35219,7 +35305,7 @@
       </c>
       <c r="P38" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35274,7 +35360,7 @@
       </c>
       <c r="P39" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35329,7 +35415,7 @@
       </c>
       <c r="P40" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35384,7 +35470,7 @@
       </c>
       <c r="P41" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35439,7 +35525,7 @@
       </c>
       <c r="P42" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36764,7 +36850,11 @@
       <c r="M66" s="5" t="n"/>
       <c r="N66" s="5" t="n"/>
       <c r="O66" s="5" t="n"/>
-      <c r="P66" s="5" t="n"/>
+      <c r="P66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="Q66" s="5" t="n"/>
       <c r="R66" s="5" t="n"/>
       <c r="S66" s="5" t="n"/>
@@ -37396,6 +37486,11 @@
       <c r="K76" s="58" t="n"/>
       <c r="L76" s="58" t="n"/>
       <c r="M76" s="58" t="n"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="59" t="inlineStr">
@@ -37613,7 +37708,7 @@
       <c r="M80" s="59" t="n"/>
       <c r="P80" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37937,7 +38032,7 @@
       </c>
       <c r="P3" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38025,7 +38120,7 @@
       </c>
       <c r="P4" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38112,7 +38207,7 @@
       </c>
       <c r="P5" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38197,7 +38292,7 @@
       </c>
       <c r="P6" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38280,7 +38375,7 @@
       </c>
       <c r="P7" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38366,7 +38461,7 @@
       </c>
       <c r="P8" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38453,7 +38548,7 @@
       </c>
       <c r="P9" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38539,7 +38634,7 @@
       </c>
       <c r="P10" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38624,7 +38719,7 @@
       </c>
       <c r="P11" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38704,7 +38799,7 @@
       </c>
       <c r="P12" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38784,7 +38879,7 @@
       </c>
       <c r="P13" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38865,7 +38960,7 @@
       </c>
       <c r="P14" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38946,7 +39041,7 @@
       </c>
       <c r="P15" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39027,7 +39122,7 @@
       </c>
       <c r="P16" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39109,7 +39204,7 @@
       </c>
       <c r="P17" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39189,7 +39284,7 @@
       </c>
       <c r="P18" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39268,7 +39363,7 @@
       </c>
       <c r="P19" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39350,7 +39445,7 @@
       </c>
       <c r="P20" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39432,7 +39527,7 @@
       </c>
       <c r="P21" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39513,7 +39608,7 @@
       </c>
       <c r="P22" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39592,7 +39687,7 @@
       </c>
       <c r="P23" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39670,7 +39765,7 @@
       </c>
       <c r="P24" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39749,7 +39844,7 @@
       </c>
       <c r="P25" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39828,7 +39923,7 @@
       </c>
       <c r="P26" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39908,7 +40003,7 @@
       </c>
       <c r="P27" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -39987,7 +40082,7 @@
       </c>
       <c r="P28" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40397,7 +40492,7 @@
       </c>
       <c r="P33" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40479,7 +40574,7 @@
       </c>
       <c r="P34" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40558,7 +40653,7 @@
       </c>
       <c r="P35" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40637,7 +40732,7 @@
       </c>
       <c r="P36" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40717,7 +40812,7 @@
       </c>
       <c r="P37" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40796,7 +40891,7 @@
       </c>
       <c r="P38" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40875,7 +40970,7 @@
       </c>
       <c r="P39" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -40954,7 +41049,7 @@
       </c>
       <c r="P40" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -41033,7 +41128,7 @@
       </c>
       <c r="P41" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -41112,7 +41207,7 @@
       </c>
       <c r="P42" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -41191,7 +41286,7 @@
       </c>
       <c r="P43" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -41270,7 +41365,7 @@
       </c>
       <c r="P44" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -41350,7 +41445,7 @@
       </c>
       <c r="P45" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -41428,6 +41523,4730 @@
         </is>
       </c>
       <c r="P46" s="70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="67" min="1" max="1"/>
+    <col width="16" customWidth="1" style="67" min="2" max="2"/>
+    <col width="40" customWidth="1" style="67" min="3" max="3"/>
+    <col width="14" customWidth="1" style="67" min="4" max="4"/>
+    <col width="40" customWidth="1" style="67" min="5" max="5"/>
+    <col width="35" customWidth="1" style="67" min="6" max="6"/>
+    <col width="40" customWidth="1" style="67" min="7" max="7"/>
+    <col width="12" customWidth="1" style="67" min="8" max="8"/>
+    <col width="15" customWidth="1" style="67" min="9" max="9"/>
+    <col width="12" customWidth="1" style="67" min="10" max="10"/>
+    <col width="12" customWidth="1" style="67" min="11" max="11"/>
+    <col width="12" customWidth="1" style="67" min="12" max="12"/>
+    <col width="15" customWidth="1" style="67" min="13" max="13"/>
+    <col width="35" customWidth="1" style="67" min="14" max="14"/>
+    <col width="45" customWidth="1" style="67" min="15" max="15"/>
+    <col width="10" customWidth="1" style="67" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Name: </t>
+        </is>
+      </c>
+      <c r="B1" s="72" t="inlineStr">
+        <is>
+          <t>Visdum 2.0 - Raw Data: Refresh Columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="67">
+      <c r="A2" s="73" t="inlineStr">
+        <is>
+          <t>Jira ID</t>
+        </is>
+      </c>
+      <c r="B2" s="73" t="inlineStr">
+        <is>
+          <t>Test Scenario ID</t>
+        </is>
+      </c>
+      <c r="C2" s="73" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D2" s="73" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="E2" s="73" t="inlineStr">
+        <is>
+          <t>Test Case Description</t>
+        </is>
+      </c>
+      <c r="F2" s="73" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="G2" s="73" t="inlineStr">
+        <is>
+          <t>Expected result</t>
+        </is>
+      </c>
+      <c r="H2" s="73" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+      <c r="I2" s="73" t="inlineStr">
+        <is>
+          <t>Actual result</t>
+        </is>
+      </c>
+      <c r="J2" s="73" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="K2" s="73" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="L2" s="73" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="M2" s="73" t="inlineStr">
+        <is>
+          <t>Comments/Issues</t>
+        </is>
+      </c>
+      <c r="N2" s="73" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="O2" s="73" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="P2" s="73" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="67">
+      <c r="A3" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B3" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C3" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns action is displayed for a standard Raw Data stream containing a Derived Column</t>
+        </is>
+      </c>
+      <c r="D3" s="74" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="E3" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns action is displayed for a standard Raw Data stream containing a Derived Column</t>
+        </is>
+      </c>
+      <c r="F3" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with at least 1 Derived Column</t>
+        </is>
+      </c>
+      <c r="G3" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns option is displayed.</t>
+        </is>
+      </c>
+      <c r="H3" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I3" s="75" t="inlineStr"/>
+      <c r="J3" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K3" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L3" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M3" s="75" t="inlineStr"/>
+      <c r="N3" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with at least 1 Derived Column</t>
+        </is>
+      </c>
+      <c r="O3" s="75" t="inlineStr">
+        <is>
+          <t>1. Open Raw Data.
+2. Locate the eligible Data Stream.
+3. Open the table-level Action menu.</t>
+        </is>
+      </c>
+      <c r="P3" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="67">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C4" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns action is displayed for a standard Raw Data stream containing a Lookup Column</t>
+        </is>
+      </c>
+      <c r="D4" s="74" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="E4" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns action is displayed for a standard Raw Data stream containing a Lookup Column</t>
+        </is>
+      </c>
+      <c r="F4" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with at least 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="G4" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns option is displayed.</t>
+        </is>
+      </c>
+      <c r="H4" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I4" s="75" t="inlineStr"/>
+      <c r="J4" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K4" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L4" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M4" s="75" t="inlineStr"/>
+      <c r="N4" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with at least 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="O4" s="75" t="inlineStr">
+        <is>
+          <t>1. Open Raw Data.
+2. Open Action menu for the stream.</t>
+        </is>
+      </c>
+      <c r="P4" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="67">
+      <c r="A5" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B5" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C5" s="75" t="inlineStr">
+        <is>
+          <t>Verify action is displayed when the stream contains both Derived and Lookup Columns</t>
+        </is>
+      </c>
+      <c r="D5" s="74" t="inlineStr">
+        <is>
+          <t>TC-03</t>
+        </is>
+      </c>
+      <c r="E5" s="75" t="inlineStr">
+        <is>
+          <t>Verify action is displayed when the stream contains both Derived and Lookup Columns</t>
+        </is>
+      </c>
+      <c r="F5" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream containing at least 1 Derived and 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="G5" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns is displayed only once.</t>
+        </is>
+      </c>
+      <c r="H5" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I5" s="75" t="inlineStr"/>
+      <c r="J5" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K5" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L5" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M5" s="75" t="inlineStr"/>
+      <c r="N5" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream containing at least 1 Derived and 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="O5" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P5" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="67">
+      <c r="A6" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C6" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns is hidden when the stream has no Derived/Lookup Columns</t>
+        </is>
+      </c>
+      <c r="D6" s="74" t="inlineStr">
+        <is>
+          <t>TC-04</t>
+        </is>
+      </c>
+      <c r="E6" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns is hidden when the stream has no Derived/Lookup Columns</t>
+        </is>
+      </c>
+      <c r="F6" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with only normal/raw columns</t>
+        </is>
+      </c>
+      <c r="G6" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns is not displayed.</t>
+        </is>
+      </c>
+      <c r="H6" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I6" s="75" t="inlineStr"/>
+      <c r="J6" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K6" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L6" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M6" s="75" t="inlineStr"/>
+      <c r="N6" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with only normal/raw columns</t>
+        </is>
+      </c>
+      <c r="O6" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P6" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="67">
+      <c r="A7" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B7" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C7" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns is hidden for a Key-Value Data Stream</t>
+        </is>
+      </c>
+      <c r="D7" s="74" t="inlineStr">
+        <is>
+          <t>TC-05</t>
+        </is>
+      </c>
+      <c r="E7" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns is hidden for a Key-Value Data Stream</t>
+        </is>
+      </c>
+      <c r="F7" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value Data Stream containing eligible column configuration if supported</t>
+        </is>
+      </c>
+      <c r="G7" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns is not displayed.</t>
+        </is>
+      </c>
+      <c r="H7" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I7" s="75" t="inlineStr"/>
+      <c r="J7" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K7" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L7" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M7" s="75" t="inlineStr"/>
+      <c r="N7" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value Data Stream containing eligible column configuration if supported</t>
+        </is>
+      </c>
+      <c r="O7" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P7" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="67">
+      <c r="A8" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B8" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C8" s="75" t="inlineStr">
+        <is>
+          <t>Verify Key-Value stream is excluded even if no/other columns are present</t>
+        </is>
+      </c>
+      <c r="D8" s="74" t="inlineStr">
+        <is>
+          <t>TC-06</t>
+        </is>
+      </c>
+      <c r="E8" s="75" t="inlineStr">
+        <is>
+          <t>Verify Key-Value stream is excluded even if no/other columns are present</t>
+        </is>
+      </c>
+      <c r="F8" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value Data Stream</t>
+        </is>
+      </c>
+      <c r="G8" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns remains unavailable.</t>
+        </is>
+      </c>
+      <c r="H8" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I8" s="75" t="inlineStr"/>
+      <c r="J8" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K8" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L8" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M8" s="75" t="inlineStr"/>
+      <c r="N8" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value Data Stream</t>
+        </is>
+      </c>
+      <c r="O8" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P8" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="67">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B9" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C9" s="75" t="inlineStr">
+        <is>
+          <t>Verify action label is exactly correct</t>
+        </is>
+      </c>
+      <c r="D9" s="74" t="inlineStr">
+        <is>
+          <t>TC-07</t>
+        </is>
+      </c>
+      <c r="E9" s="75" t="inlineStr">
+        <is>
+          <t>Verify action label is exactly correct</t>
+        </is>
+      </c>
+      <c r="F9" s="75" t="inlineStr">
+        <is>
+          <t>Eligible standard Raw Data stream</t>
+        </is>
+      </c>
+      <c r="G9" s="75" t="inlineStr">
+        <is>
+          <t>Label appears as Refresh Columns.</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I9" s="75" t="inlineStr"/>
+      <c r="J9" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K9" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M9" s="75" t="inlineStr"/>
+      <c r="N9" s="75" t="inlineStr">
+        <is>
+          <t>Eligible standard Raw Data stream</t>
+        </is>
+      </c>
+      <c r="O9" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P9" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="67">
+      <c r="A10" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B10" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C10" s="75" t="inlineStr">
+        <is>
+          <t>Verify no existing Action menu options are changed</t>
+        </is>
+      </c>
+      <c r="D10" s="74" t="inlineStr">
+        <is>
+          <t>TC-08</t>
+        </is>
+      </c>
+      <c r="E10" s="75" t="inlineStr">
+        <is>
+          <t>Verify no existing Action menu options are changed</t>
+        </is>
+      </c>
+      <c r="F10" s="75" t="inlineStr">
+        <is>
+          <t>Existing Raw Data stream</t>
+        </is>
+      </c>
+      <c r="G10" s="75" t="inlineStr">
+        <is>
+          <t>Existing actions remain unchanged in label/functionality.</t>
+        </is>
+      </c>
+      <c r="H10" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I10" s="75" t="inlineStr"/>
+      <c r="J10" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K10" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M10" s="75" t="inlineStr"/>
+      <c r="N10" s="75" t="inlineStr">
+        <is>
+          <t>Existing Raw Data stream</t>
+        </is>
+      </c>
+      <c r="O10" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu before/after feature availability.</t>
+        </is>
+      </c>
+      <c r="P10" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="67">
+      <c r="A11" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B11" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C11" s="75" t="inlineStr">
+        <is>
+          <t>Open confirmation modal by clicking Refresh Columns</t>
+        </is>
+      </c>
+      <c r="D11" s="74" t="inlineStr">
+        <is>
+          <t>TC-09</t>
+        </is>
+      </c>
+      <c r="E11" s="75" t="inlineStr">
+        <is>
+          <t>Open confirmation modal by clicking Refresh Columns</t>
+        </is>
+      </c>
+      <c r="F11" s="75" t="inlineStr">
+        <is>
+          <t>Eligible Data Stream with Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="G11" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal opens.</t>
+        </is>
+      </c>
+      <c r="H11" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I11" s="75" t="inlineStr"/>
+      <c r="J11" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K11" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M11" s="75" t="inlineStr"/>
+      <c r="N11" s="75" t="inlineStr">
+        <is>
+          <t>Eligible Data Stream with Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="O11" s="75" t="inlineStr">
+        <is>
+          <t>1. Open Action menu.
+2. Click Refresh Columns.</t>
+        </is>
+      </c>
+      <c r="P11" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="67">
+      <c r="A12" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B12" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C12" s="75" t="inlineStr">
+        <is>
+          <t>Verify confirmation message</t>
+        </is>
+      </c>
+      <c r="D12" s="74" t="inlineStr">
+        <is>
+          <t>TC-10</t>
+        </is>
+      </c>
+      <c r="E12" s="75" t="inlineStr">
+        <is>
+          <t>Verify confirmation message</t>
+        </is>
+      </c>
+      <c r="F12" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G12" s="75" t="inlineStr">
+        <is>
+          <t>Message is exactly: “Are you sure you want to refresh all Derived and Lookup Column values?”</t>
+        </is>
+      </c>
+      <c r="H12" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I12" s="75" t="inlineStr"/>
+      <c r="J12" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K12" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L12" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M12" s="75" t="inlineStr"/>
+      <c r="N12" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O12" s="75" t="inlineStr">
+        <is>
+          <t>Read modal content.</t>
+        </is>
+      </c>
+      <c r="P12" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="67">
+      <c r="A13" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B13" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C13" s="75" t="inlineStr">
+        <is>
+          <t>Verify Cancel button is displayed and secondary/lighter</t>
+        </is>
+      </c>
+      <c r="D13" s="74" t="inlineStr">
+        <is>
+          <t>TC-11</t>
+        </is>
+      </c>
+      <c r="E13" s="75" t="inlineStr">
+        <is>
+          <t>Verify Cancel button is displayed and secondary/lighter</t>
+        </is>
+      </c>
+      <c r="F13" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G13" s="75" t="inlineStr">
+        <is>
+          <t>Cancel is displayed as secondary/lighter action.</t>
+        </is>
+      </c>
+      <c r="H13" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I13" s="75" t="inlineStr"/>
+      <c r="J13" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K13" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L13" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M13" s="75" t="inlineStr"/>
+      <c r="N13" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O13" s="75" t="inlineStr">
+        <is>
+          <t>Observe buttons.</t>
+        </is>
+      </c>
+      <c r="P13" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="67">
+      <c r="A14" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B14" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C14" s="75" t="inlineStr">
+        <is>
+          <t>Verify Submit button is displayed and primary/darker</t>
+        </is>
+      </c>
+      <c r="D14" s="74" t="inlineStr">
+        <is>
+          <t>TC-12</t>
+        </is>
+      </c>
+      <c r="E14" s="75" t="inlineStr">
+        <is>
+          <t>Verify Submit button is displayed and primary/darker</t>
+        </is>
+      </c>
+      <c r="F14" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G14" s="75" t="inlineStr">
+        <is>
+          <t>Submit is displayed as primary/darker action.</t>
+        </is>
+      </c>
+      <c r="H14" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I14" s="75" t="inlineStr"/>
+      <c r="J14" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K14" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L14" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M14" s="75" t="inlineStr"/>
+      <c r="N14" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O14" s="75" t="inlineStr">
+        <is>
+          <t>Observe buttons.</t>
+        </is>
+      </c>
+      <c r="P14" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="67">
+      <c r="A15" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B15" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C15" s="75" t="inlineStr">
+        <is>
+          <t>Verify Cancel closes confirmation modal without processing</t>
+        </is>
+      </c>
+      <c r="D15" s="74" t="inlineStr">
+        <is>
+          <t>TC-13</t>
+        </is>
+      </c>
+      <c r="E15" s="75" t="inlineStr">
+        <is>
+          <t>Verify Cancel closes confirmation modal without processing</t>
+        </is>
+      </c>
+      <c r="F15" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G15" s="75" t="inlineStr">
+        <is>
+          <t>Modal closes and no processing starts.</t>
+        </is>
+      </c>
+      <c r="H15" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I15" s="75" t="inlineStr"/>
+      <c r="J15" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K15" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M15" s="75" t="inlineStr"/>
+      <c r="N15" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O15" s="75" t="inlineStr">
+        <is>
+          <t>Click Cancel.</t>
+        </is>
+      </c>
+      <c r="P15" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" s="67">
+      <c r="A16" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B16" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C16" s="75" t="inlineStr">
+        <is>
+          <t>Verify clicking outside/close icon behavior</t>
+        </is>
+      </c>
+      <c r="D16" s="74" t="inlineStr">
+        <is>
+          <t>TC-14</t>
+        </is>
+      </c>
+      <c r="E16" s="75" t="inlineStr">
+        <is>
+          <t>Verify clicking outside/close icon behavior</t>
+        </is>
+      </c>
+      <c r="F16" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G16" s="75" t="inlineStr">
+        <is>
+          <t>Modal closes according to existing modal behavior and processing does not start.</t>
+        </is>
+      </c>
+      <c r="H16" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I16" s="75" t="inlineStr"/>
+      <c r="J16" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M16" s="75" t="inlineStr"/>
+      <c r="N16" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O16" s="75" t="inlineStr">
+        <is>
+          <t>Click supported close control/outside modal if standard behavior exists.</t>
+        </is>
+      </c>
+      <c r="P16" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="67">
+      <c r="A17" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B17" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C17" s="75" t="inlineStr">
+        <is>
+          <t>Verify Submit starts bulk column refresh</t>
+        </is>
+      </c>
+      <c r="D17" s="74" t="inlineStr">
+        <is>
+          <t>TC-15</t>
+        </is>
+      </c>
+      <c r="E17" s="75" t="inlineStr">
+        <is>
+          <t>Verify Submit starts bulk column refresh</t>
+        </is>
+      </c>
+      <c r="F17" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="G17" s="75" t="inlineStr">
+        <is>
+          <t>Processing starts for all applicable columns.</t>
+        </is>
+      </c>
+      <c r="H17" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I17" s="75" t="inlineStr"/>
+      <c r="J17" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M17" s="75" t="inlineStr"/>
+      <c r="N17" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="O17" s="75" t="inlineStr">
+        <is>
+          <t>1. Open Refresh Columns.
+2. Click Submit.</t>
+        </is>
+      </c>
+      <c r="P17" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="67">
+      <c r="A18" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B18" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C18" s="75" t="inlineStr">
+        <is>
+          <t>Verify all Derived Columns are included in refresh</t>
+        </is>
+      </c>
+      <c r="D18" s="74" t="inlineStr">
+        <is>
+          <t>TC-16</t>
+        </is>
+      </c>
+      <c r="E18" s="75" t="inlineStr">
+        <is>
+          <t>Verify all Derived Columns are included in refresh</t>
+        </is>
+      </c>
+      <c r="F18" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Derived Columns</t>
+        </is>
+      </c>
+      <c r="G18" s="75" t="inlineStr">
+        <is>
+          <t>Every Derived Column belonging to the selected stream is processed.</t>
+        </is>
+      </c>
+      <c r="H18" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I18" s="75" t="inlineStr"/>
+      <c r="J18" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K18" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M18" s="75" t="inlineStr"/>
+      <c r="N18" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Derived Columns</t>
+        </is>
+      </c>
+      <c r="O18" s="75" t="inlineStr">
+        <is>
+          <t>Trigger Refresh Columns and monitor processing/result.</t>
+        </is>
+      </c>
+      <c r="P18" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="67">
+      <c r="A19" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B19" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C19" s="75" t="inlineStr">
+        <is>
+          <t>Verify all Lookup Columns are included in refresh</t>
+        </is>
+      </c>
+      <c r="D19" s="74" t="inlineStr">
+        <is>
+          <t>TC-17</t>
+        </is>
+      </c>
+      <c r="E19" s="75" t="inlineStr">
+        <is>
+          <t>Verify all Lookup Columns are included in refresh</t>
+        </is>
+      </c>
+      <c r="F19" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Lookup Columns</t>
+        </is>
+      </c>
+      <c r="G19" s="75" t="inlineStr">
+        <is>
+          <t>Every Lookup Column belonging to the selected stream is processed.</t>
+        </is>
+      </c>
+      <c r="H19" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I19" s="75" t="inlineStr"/>
+      <c r="J19" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K19" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L19" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M19" s="75" t="inlineStr"/>
+      <c r="N19" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Lookup Columns</t>
+        </is>
+      </c>
+      <c r="O19" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P19" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" s="67">
+      <c r="A20" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B20" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C20" s="75" t="inlineStr">
+        <is>
+          <t>Verify both Derived and Lookup Columns are processed together</t>
+        </is>
+      </c>
+      <c r="D20" s="74" t="inlineStr">
+        <is>
+          <t>TC-18</t>
+        </is>
+      </c>
+      <c r="E20" s="75" t="inlineStr">
+        <is>
+          <t>Verify both Derived and Lookup Columns are processed together</t>
+        </is>
+      </c>
+      <c r="F20" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 3 Derived + 2 Lookup columns</t>
+        </is>
+      </c>
+      <c r="G20" s="75" t="inlineStr">
+        <is>
+          <t>All 5 eligible columns are processed.</t>
+        </is>
+      </c>
+      <c r="H20" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I20" s="75" t="inlineStr"/>
+      <c r="J20" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K20" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L20" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M20" s="75" t="inlineStr"/>
+      <c r="N20" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 3 Derived + 2 Lookup columns</t>
+        </is>
+      </c>
+      <c r="O20" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P20" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="67">
+      <c r="A21" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B21" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C21" s="75" t="inlineStr">
+        <is>
+          <t>Verify normal/raw columns are not treated as Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="D21" s="74" t="inlineStr">
+        <is>
+          <t>TC-19</t>
+        </is>
+      </c>
+      <c r="E21" s="75" t="inlineStr">
+        <is>
+          <t>Verify normal/raw columns are not treated as Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="F21" s="75" t="inlineStr">
+        <is>
+          <t>Stream has raw + Derived + Lookup columns</t>
+        </is>
+      </c>
+      <c r="G21" s="75" t="inlineStr">
+        <is>
+          <t>Raw columns are not included in Derived/Lookup processing count.</t>
+        </is>
+      </c>
+      <c r="H21" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I21" s="75" t="inlineStr"/>
+      <c r="J21" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K21" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L21" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M21" s="75" t="inlineStr"/>
+      <c r="N21" s="75" t="inlineStr">
+        <is>
+          <t>Stream has raw + Derived + Lookup columns</t>
+        </is>
+      </c>
+      <c r="O21" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P21" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="67">
+      <c r="A22" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B22" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C22" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh is scoped to selected Data Stream</t>
+        </is>
+      </c>
+      <c r="D22" s="74" t="inlineStr">
+        <is>
+          <t>TC-20</t>
+        </is>
+      </c>
+      <c r="E22" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh is scoped to selected Data Stream</t>
+        </is>
+      </c>
+      <c r="F22" s="75" t="inlineStr">
+        <is>
+          <t>Data Stream A and B both have Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="G22" s="75" t="inlineStr">
+        <is>
+          <t>Only A is processed. B remains unaffected.</t>
+        </is>
+      </c>
+      <c r="H22" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I22" s="75" t="inlineStr"/>
+      <c r="J22" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K22" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L22" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M22" s="75" t="inlineStr"/>
+      <c r="N22" s="75" t="inlineStr">
+        <is>
+          <t>Data Stream A and B both have Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="O22" s="75" t="inlineStr">
+        <is>
+          <t>1. Trigger refresh from A.
+2. Check processing/activity/data for B.</t>
+        </is>
+      </c>
+      <c r="P22" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="67">
+      <c r="A23" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B23" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C23" s="75" t="inlineStr">
+        <is>
+          <t>Verify unrelated Data Stream is not synchronized</t>
+        </is>
+      </c>
+      <c r="D23" s="74" t="inlineStr">
+        <is>
+          <t>TC-21</t>
+        </is>
+      </c>
+      <c r="E23" s="75" t="inlineStr">
+        <is>
+          <t>Verify unrelated Data Stream is not synchronized</t>
+        </is>
+      </c>
+      <c r="F23" s="75" t="inlineStr">
+        <is>
+          <t>Two independent Data Streams exist</t>
+        </is>
+      </c>
+      <c r="G23" s="75" t="inlineStr">
+        <is>
+          <t>No fetch/upload/sync is triggered for Data Stream B.</t>
+        </is>
+      </c>
+      <c r="H23" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I23" s="75" t="inlineStr"/>
+      <c r="J23" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K23" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L23" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M23" s="75" t="inlineStr"/>
+      <c r="N23" s="75" t="inlineStr">
+        <is>
+          <t>Two independent Data Streams exist</t>
+        </is>
+      </c>
+      <c r="O23" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh on Data Stream A.</t>
+        </is>
+      </c>
+      <c r="P23" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="67">
+      <c r="A24" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B24" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C24" s="75" t="inlineStr">
+        <is>
+          <t>Verify processing is asynchronous</t>
+        </is>
+      </c>
+      <c r="D24" s="74" t="inlineStr">
+        <is>
+          <t>TC-22</t>
+        </is>
+      </c>
+      <c r="E24" s="75" t="inlineStr">
+        <is>
+          <t>Verify processing is asynchronous</t>
+        </is>
+      </c>
+      <c r="F24" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream with sufficient records</t>
+        </is>
+      </c>
+      <c r="G24" s="75" t="inlineStr">
+        <is>
+          <t>User receives processing state/modal and UI is not forced to wait for synchronous completion.</t>
+        </is>
+      </c>
+      <c r="H24" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I24" s="75" t="inlineStr"/>
+      <c r="J24" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K24" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L24" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M24" s="75" t="inlineStr"/>
+      <c r="N24" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream with sufficient records</t>
+        </is>
+      </c>
+      <c r="O24" s="75" t="inlineStr">
+        <is>
+          <t>Click Submit.</t>
+        </is>
+      </c>
+      <c r="P24" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="67">
+      <c r="A25" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B25" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C25" s="75" t="inlineStr">
+        <is>
+          <t>Verify standard processing modal is displayed</t>
+        </is>
+      </c>
+      <c r="D25" s="74" t="inlineStr">
+        <is>
+          <t>TC-23</t>
+        </is>
+      </c>
+      <c r="E25" s="75" t="inlineStr">
+        <is>
+          <t>Verify standard processing modal is displayed</t>
+        </is>
+      </c>
+      <c r="F25" s="75" t="inlineStr">
+        <is>
+          <t>Submit refresh request</t>
+        </is>
+      </c>
+      <c r="G25" s="75" t="inlineStr">
+        <is>
+          <t>Same processing modal/experience used by existing Derived/Lookup processing is displayed.</t>
+        </is>
+      </c>
+      <c r="H25" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I25" s="75" t="inlineStr"/>
+      <c r="J25" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K25" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L25" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M25" s="75" t="inlineStr"/>
+      <c r="N25" s="75" t="inlineStr">
+        <is>
+          <t>Submit refresh request</t>
+        </is>
+      </c>
+      <c r="O25" s="75" t="inlineStr">
+        <is>
+          <t>Click Submit.</t>
+        </is>
+      </c>
+      <c r="P25" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1" s="67">
+      <c r="A26" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B26" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C26" s="75" t="inlineStr">
+        <is>
+          <t>Verify processing modal shows running state</t>
+        </is>
+      </c>
+      <c r="D26" s="74" t="inlineStr">
+        <is>
+          <t>TC-24</t>
+        </is>
+      </c>
+      <c r="E26" s="75" t="inlineStr">
+        <is>
+          <t>Verify processing modal shows running state</t>
+        </is>
+      </c>
+      <c r="F26" s="75" t="inlineStr">
+        <is>
+          <t>Processing in progress</t>
+        </is>
+      </c>
+      <c r="G26" s="75" t="inlineStr">
+        <is>
+          <t>Modal indicates processing is in progress using existing experience.</t>
+        </is>
+      </c>
+      <c r="H26" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I26" s="75" t="inlineStr"/>
+      <c r="J26" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K26" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L26" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M26" s="75" t="inlineStr"/>
+      <c r="N26" s="75" t="inlineStr">
+        <is>
+          <t>Processing in progress</t>
+        </is>
+      </c>
+      <c r="O26" s="75" t="inlineStr">
+        <is>
+          <t>Observe processing modal.</t>
+        </is>
+      </c>
+      <c r="P26" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1" s="67">
+      <c r="A27" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B27" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C27" s="75" t="inlineStr">
+        <is>
+          <t>Verify user can leave processing modal without stopping job</t>
+        </is>
+      </c>
+      <c r="D27" s="74" t="inlineStr">
+        <is>
+          <t>TC-25</t>
+        </is>
+      </c>
+      <c r="E27" s="75" t="inlineStr">
+        <is>
+          <t>Verify user can leave processing modal without stopping job</t>
+        </is>
+      </c>
+      <c r="F27" s="75" t="inlineStr">
+        <is>
+          <t>Processing has started</t>
+        </is>
+      </c>
+      <c r="G27" s="75" t="inlineStr">
+        <is>
+          <t>Processing continues asynchronously in background.</t>
+        </is>
+      </c>
+      <c r="H27" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I27" s="75" t="inlineStr"/>
+      <c r="J27" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K27" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L27" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M27" s="75" t="inlineStr"/>
+      <c r="N27" s="75" t="inlineStr">
+        <is>
+          <t>Processing has started</t>
+        </is>
+      </c>
+      <c r="O27" s="75" t="inlineStr">
+        <is>
+          <t>Navigate away/close modal using supported behavior.</t>
+        </is>
+      </c>
+      <c r="P27" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" s="67">
+      <c r="A28" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B28" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C28" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh continues after closing processing modal</t>
+        </is>
+      </c>
+      <c r="D28" s="74" t="inlineStr">
+        <is>
+          <t>TC-26</t>
+        </is>
+      </c>
+      <c r="E28" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh continues after closing processing modal</t>
+        </is>
+      </c>
+      <c r="F28" s="75" t="inlineStr">
+        <is>
+          <t>Processing is active</t>
+        </is>
+      </c>
+      <c r="G28" s="75" t="inlineStr">
+        <is>
+          <t>Backend processing completes successfully even though modal is no longer open.</t>
+        </is>
+      </c>
+      <c r="H28" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I28" s="75" t="inlineStr"/>
+      <c r="J28" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K28" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L28" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M28" s="75" t="inlineStr"/>
+      <c r="N28" s="75" t="inlineStr">
+        <is>
+          <t>Processing is active</t>
+        </is>
+      </c>
+      <c r="O28" s="75" t="inlineStr">
+        <is>
+          <t>Close/minimize processing experience, then wait for processing completion.</t>
+        </is>
+      </c>
+      <c r="P28" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="67">
+      <c r="A29" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B29" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C29" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion modal appears when user remains on processing modal</t>
+        </is>
+      </c>
+      <c r="D29" s="74" t="inlineStr">
+        <is>
+          <t>TC-27</t>
+        </is>
+      </c>
+      <c r="E29" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion modal appears when user remains on processing modal</t>
+        </is>
+      </c>
+      <c r="F29" s="75" t="inlineStr">
+        <is>
+          <t>User remains on processing modal until completion</t>
+        </is>
+      </c>
+      <c r="G29" s="75" t="inlineStr">
+        <is>
+          <t>Processing state changes to completion modal/state.</t>
+        </is>
+      </c>
+      <c r="H29" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I29" s="75" t="inlineStr"/>
+      <c r="J29" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K29" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L29" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M29" s="75" t="inlineStr"/>
+      <c r="N29" s="75" t="inlineStr">
+        <is>
+          <t>User remains on processing modal until completion</t>
+        </is>
+      </c>
+      <c r="O29" s="75" t="inlineStr">
+        <is>
+          <t>Wait for processing to finish.</t>
+        </is>
+      </c>
+      <c r="P29" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="67">
+      <c r="A30" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B30" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C30" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Columns processed count</t>
+        </is>
+      </c>
+      <c r="D30" s="74" t="inlineStr">
+        <is>
+          <t>TC-28</t>
+        </is>
+      </c>
+      <c r="E30" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Columns processed count</t>
+        </is>
+      </c>
+      <c r="F30" s="75" t="inlineStr">
+        <is>
+          <t>Example: 3 Derived Columns</t>
+        </is>
+      </c>
+      <c r="G30" s="75" t="inlineStr">
+        <is>
+          <t>Completion modal displays Derived Columns Processed: 3.</t>
+        </is>
+      </c>
+      <c r="H30" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I30" s="75" t="inlineStr"/>
+      <c r="J30" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K30" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L30" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M30" s="75" t="inlineStr"/>
+      <c r="N30" s="75" t="inlineStr">
+        <is>
+          <t>Example: 3 Derived Columns</t>
+        </is>
+      </c>
+      <c r="O30" s="75" t="inlineStr">
+        <is>
+          <t>Complete refresh.</t>
+        </is>
+      </c>
+      <c r="P30" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="67">
+      <c r="A31" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B31" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C31" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup Columns processed count</t>
+        </is>
+      </c>
+      <c r="D31" s="74" t="inlineStr">
+        <is>
+          <t>TC-29</t>
+        </is>
+      </c>
+      <c r="E31" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup Columns processed count</t>
+        </is>
+      </c>
+      <c r="F31" s="75" t="inlineStr">
+        <is>
+          <t>Example: 2 Lookup Columns</t>
+        </is>
+      </c>
+      <c r="G31" s="75" t="inlineStr">
+        <is>
+          <t>Completion modal displays Lookup Columns Processed: 2.</t>
+        </is>
+      </c>
+      <c r="H31" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I31" s="75" t="inlineStr"/>
+      <c r="J31" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K31" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L31" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M31" s="75" t="inlineStr"/>
+      <c r="N31" s="75" t="inlineStr">
+        <is>
+          <t>Example: 2 Lookup Columns</t>
+        </is>
+      </c>
+      <c r="O31" s="75" t="inlineStr">
+        <is>
+          <t>Complete refresh.</t>
+        </is>
+      </c>
+      <c r="P31" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="67">
+      <c r="A32" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B32" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C32" s="75" t="inlineStr">
+        <is>
+          <t>Verify Records Processed count</t>
+        </is>
+      </c>
+      <c r="D32" s="74" t="inlineStr">
+        <is>
+          <t>TC-30</t>
+        </is>
+      </c>
+      <c r="E32" s="75" t="inlineStr">
+        <is>
+          <t>Verify Records Processed count</t>
+        </is>
+      </c>
+      <c r="F32" s="75" t="inlineStr">
+        <is>
+          <t>Known dataset, e.g. 10,240 records</t>
+        </is>
+      </c>
+      <c r="G32" s="75" t="inlineStr">
+        <is>
+          <t>Count matches actual number of records processed.</t>
+        </is>
+      </c>
+      <c r="H32" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I32" s="75" t="inlineStr"/>
+      <c r="J32" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K32" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L32" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M32" s="75" t="inlineStr"/>
+      <c r="N32" s="75" t="inlineStr">
+        <is>
+          <t>Known dataset, e.g. 10,240 records</t>
+        </is>
+      </c>
+      <c r="O32" s="75" t="inlineStr">
+        <is>
+          <t>Complete refresh.</t>
+        </is>
+      </c>
+      <c r="P32" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="67">
+      <c r="A33" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B33" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C33" s="75" t="inlineStr">
+        <is>
+          <t>Verify Records Updated count</t>
+        </is>
+      </c>
+      <c r="D33" s="74" t="inlineStr">
+        <is>
+          <t>TC-31</t>
+        </is>
+      </c>
+      <c r="E33" s="75" t="inlineStr">
+        <is>
+          <t>Verify Records Updated count</t>
+        </is>
+      </c>
+      <c r="F33" s="75" t="inlineStr">
+        <is>
+          <t>Dataset where known records change after refresh</t>
+        </is>
+      </c>
+      <c r="G33" s="75" t="inlineStr">
+        <is>
+          <t>Count matches actual records whose values were updated.</t>
+        </is>
+      </c>
+      <c r="H33" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I33" s="75" t="inlineStr"/>
+      <c r="J33" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K33" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L33" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M33" s="75" t="inlineStr"/>
+      <c r="N33" s="75" t="inlineStr">
+        <is>
+          <t>Dataset where known records change after refresh</t>
+        </is>
+      </c>
+      <c r="O33" s="75" t="inlineStr">
+        <is>
+          <t>Complete refresh.</t>
+        </is>
+      </c>
+      <c r="P33" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="67">
+      <c r="A34" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B34" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C34" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts when no values change</t>
+        </is>
+      </c>
+      <c r="D34" s="74" t="inlineStr">
+        <is>
+          <t>TC-32</t>
+        </is>
+      </c>
+      <c r="E34" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts when no values change</t>
+        </is>
+      </c>
+      <c r="F34" s="75" t="inlineStr">
+        <is>
+          <t>Source values already match calculated/lookup values</t>
+        </is>
+      </c>
+      <c r="G34" s="75" t="inlineStr">
+        <is>
+          <t>Records Processed reflects processed records and Records Updated reflects 0 where applicable.</t>
+        </is>
+      </c>
+      <c r="H34" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I34" s="75" t="inlineStr"/>
+      <c r="J34" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K34" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L34" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M34" s="75" t="inlineStr"/>
+      <c r="N34" s="75" t="inlineStr">
+        <is>
+          <t>Source values already match calculated/lookup values</t>
+        </is>
+      </c>
+      <c r="O34" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P34" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="67">
+      <c r="A35" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B35" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C35" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts when all records change</t>
+        </is>
+      </c>
+      <c r="D35" s="74" t="inlineStr">
+        <is>
+          <t>TC-33</t>
+        </is>
+      </c>
+      <c r="E35" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts when all records change</t>
+        </is>
+      </c>
+      <c r="F35" s="75" t="inlineStr">
+        <is>
+          <t>Modify source values so all applicable values change</t>
+        </is>
+      </c>
+      <c r="G35" s="75" t="inlineStr">
+        <is>
+          <t>Records Updated reflects actual updated records.</t>
+        </is>
+      </c>
+      <c r="H35" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I35" s="75" t="inlineStr"/>
+      <c r="J35" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K35" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L35" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M35" s="75" t="inlineStr"/>
+      <c r="N35" s="75" t="inlineStr">
+        <is>
+          <t>Modify source values so all applicable values change</t>
+        </is>
+      </c>
+      <c r="O35" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P35" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="67">
+      <c r="A36" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B36" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C36" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts for mixed updated/non-updated records</t>
+        </is>
+      </c>
+      <c r="D36" s="74" t="inlineStr">
+        <is>
+          <t>TC-34</t>
+        </is>
+      </c>
+      <c r="E36" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts for mixed updated/non-updated records</t>
+        </is>
+      </c>
+      <c r="F36" s="75" t="inlineStr">
+        <is>
+          <t>Dataset with some changed and some unchanged records</t>
+        </is>
+      </c>
+      <c r="G36" s="75" t="inlineStr">
+        <is>
+          <t>Updated count includes only actually updated records.</t>
+        </is>
+      </c>
+      <c r="H36" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I36" s="75" t="inlineStr"/>
+      <c r="J36" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K36" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L36" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M36" s="75" t="inlineStr"/>
+      <c r="N36" s="75" t="inlineStr">
+        <is>
+          <t>Dataset with some changed and some unchanged records</t>
+        </is>
+      </c>
+      <c r="O36" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P36" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1" s="67">
+      <c r="A37" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B37" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C37" s="75" t="inlineStr">
+        <is>
+          <t>Verify async locking blocks conflicting process</t>
+        </is>
+      </c>
+      <c r="D37" s="74" t="inlineStr">
+        <is>
+          <t>TC-35</t>
+        </is>
+      </c>
+      <c r="E37" s="75" t="inlineStr">
+        <is>
+          <t>Verify async locking blocks conflicting process</t>
+        </is>
+      </c>
+      <c r="F37" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns processing is running</t>
+        </is>
+      </c>
+      <c r="G37" s="75" t="inlineStr">
+        <is>
+          <t>Conflicting process is blocked according to existing async locking behavior.</t>
+        </is>
+      </c>
+      <c r="H37" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I37" s="75" t="inlineStr"/>
+      <c r="J37" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K37" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L37" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M37" s="75" t="inlineStr"/>
+      <c r="N37" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns processing is running</t>
+        </is>
+      </c>
+      <c r="O37" s="75" t="inlineStr">
+        <is>
+          <t>Attempt another conflicting async process.</t>
+        </is>
+      </c>
+      <c r="P37" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="67">
+      <c r="A38" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B38" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C38" s="75" t="inlineStr">
+        <is>
+          <t>Verify another conflicting process cannot bypass lock from another UI action</t>
+        </is>
+      </c>
+      <c r="D38" s="74" t="inlineStr">
+        <is>
+          <t>TC-36</t>
+        </is>
+      </c>
+      <c r="E38" s="75" t="inlineStr">
+        <is>
+          <t>Verify another conflicting process cannot bypass lock from another UI action</t>
+        </is>
+      </c>
+      <c r="F38" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is in progress</t>
+        </is>
+      </c>
+      <c r="G38" s="75" t="inlineStr">
+        <is>
+          <t>Operation is blocked by existing async-process lock.</t>
+        </is>
+      </c>
+      <c r="H38" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I38" s="75" t="inlineStr"/>
+      <c r="J38" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K38" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L38" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M38" s="75" t="inlineStr"/>
+      <c r="N38" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is in progress</t>
+        </is>
+      </c>
+      <c r="O38" s="75" t="inlineStr">
+        <is>
+          <t>Attempt supported conflicting operation from another page/action.</t>
+        </is>
+      </c>
+      <c r="P38" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="67">
+      <c r="A39" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B39" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C39" s="75" t="inlineStr">
+        <is>
+          <t>Verify non-conflicting operations follow existing locking behavior</t>
+        </is>
+      </c>
+      <c r="D39" s="74" t="inlineStr">
+        <is>
+          <t>TC-37</t>
+        </is>
+      </c>
+      <c r="E39" s="75" t="inlineStr">
+        <is>
+          <t>Verify non-conflicting operations follow existing locking behavior</t>
+        </is>
+      </c>
+      <c r="F39" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is running</t>
+        </is>
+      </c>
+      <c r="G39" s="75" t="inlineStr">
+        <is>
+          <t>Behavior follows existing async processing rules; no unexpected blocking.</t>
+        </is>
+      </c>
+      <c r="H39" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I39" s="75" t="inlineStr"/>
+      <c r="J39" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K39" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L39" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M39" s="75" t="inlineStr"/>
+      <c r="N39" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is running</t>
+        </is>
+      </c>
+      <c r="O39" s="75" t="inlineStr">
+        <is>
+          <t>Attempt unrelated/non-conflicting operation.</t>
+        </is>
+      </c>
+      <c r="P39" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="67">
+      <c r="A40" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B40" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C40" s="75" t="inlineStr">
+        <is>
+          <t>Verify only one refresh can be initiated for the same stream while processing</t>
+        </is>
+      </c>
+      <c r="D40" s="74" t="inlineStr">
+        <is>
+          <t>TC-38</t>
+        </is>
+      </c>
+      <c r="E40" s="75" t="inlineStr">
+        <is>
+          <t>Verify only one refresh can be initiated for the same stream while processing</t>
+        </is>
+      </c>
+      <c r="F40" s="75" t="inlineStr">
+        <is>
+          <t>Refresh already running</t>
+        </is>
+      </c>
+      <c r="G40" s="75" t="inlineStr">
+        <is>
+          <t>Second conflicting refresh is prevented according to locking behavior.</t>
+        </is>
+      </c>
+      <c r="H40" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I40" s="75" t="inlineStr"/>
+      <c r="J40" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K40" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L40" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M40" s="75" t="inlineStr"/>
+      <c r="N40" s="75" t="inlineStr">
+        <is>
+          <t>Refresh already running</t>
+        </is>
+      </c>
+      <c r="O40" s="75" t="inlineStr">
+        <is>
+          <t>Attempt Refresh Columns again.</t>
+        </is>
+      </c>
+      <c r="P40" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="67">
+      <c r="A41" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B41" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C41" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Column calculation logic is unchanged</t>
+        </is>
+      </c>
+      <c r="D41" s="74" t="inlineStr">
+        <is>
+          <t>TC-39</t>
+        </is>
+      </c>
+      <c r="E41" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Column calculation logic is unchanged</t>
+        </is>
+      </c>
+      <c r="F41" s="75" t="inlineStr">
+        <is>
+          <t>Existing Derived Column test data</t>
+        </is>
+      </c>
+      <c r="G41" s="75" t="inlineStr">
+        <is>
+          <t>Calculated values remain correct and unchanged.</t>
+        </is>
+      </c>
+      <c r="H41" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I41" s="75" t="inlineStr"/>
+      <c r="J41" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K41" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L41" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M41" s="75" t="inlineStr"/>
+      <c r="N41" s="75" t="inlineStr">
+        <is>
+          <t>Existing Derived Column test data</t>
+        </is>
+      </c>
+      <c r="O41" s="75" t="inlineStr">
+        <is>
+          <t>Run normal Derived Column calculation and compare with pre-feature behavior.</t>
+        </is>
+      </c>
+      <c r="P41" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="67">
+      <c r="A42" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B42" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C42" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup Column resolution logic is unchanged</t>
+        </is>
+      </c>
+      <c r="D42" s="74" t="inlineStr">
+        <is>
+          <t>TC-40</t>
+        </is>
+      </c>
+      <c r="E42" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup Column resolution logic is unchanged</t>
+        </is>
+      </c>
+      <c r="F42" s="75" t="inlineStr">
+        <is>
+          <t>Existing Lookup setup with known mappings</t>
+        </is>
+      </c>
+      <c r="G42" s="75" t="inlineStr">
+        <is>
+          <t>Lookup values resolve exactly according to existing logic.</t>
+        </is>
+      </c>
+      <c r="H42" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I42" s="75" t="inlineStr"/>
+      <c r="J42" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K42" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L42" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M42" s="75" t="inlineStr"/>
+      <c r="N42" s="75" t="inlineStr">
+        <is>
+          <t>Existing Lookup setup with known mappings</t>
+        </is>
+      </c>
+      <c r="O42" s="75" t="inlineStr">
+        <is>
+          <t>Run refresh and compare values.</t>
+        </is>
+      </c>
+      <c r="P42" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="67">
+      <c r="A43" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B43" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C43" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Column dependencies still work</t>
+        </is>
+      </c>
+      <c r="D43" s="74" t="inlineStr">
+        <is>
+          <t>TC-41</t>
+        </is>
+      </c>
+      <c r="E43" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Column dependencies still work</t>
+        </is>
+      </c>
+      <c r="F43" s="75" t="inlineStr">
+        <is>
+          <t>Derived Column A depends on another field/column</t>
+        </is>
+      </c>
+      <c r="G43" s="75" t="inlineStr">
+        <is>
+          <t>Dependent Derived Column recalculates correctly using existing dependency logic.</t>
+        </is>
+      </c>
+      <c r="H43" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I43" s="75" t="inlineStr"/>
+      <c r="J43" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K43" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L43" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M43" s="75" t="inlineStr"/>
+      <c r="N43" s="75" t="inlineStr">
+        <is>
+          <t>Derived Column A depends on another field/column</t>
+        </is>
+      </c>
+      <c r="O43" s="75" t="inlineStr">
+        <is>
+          <t>Change source value and run refresh.</t>
+        </is>
+      </c>
+      <c r="P43" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="67">
+      <c r="A44" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B44" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C44" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup dependency/source behavior remains unchanged</t>
+        </is>
+      </c>
+      <c r="D44" s="74" t="inlineStr">
+        <is>
+          <t>TC-42</t>
+        </is>
+      </c>
+      <c r="E44" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup dependency/source behavior remains unchanged</t>
+        </is>
+      </c>
+      <c r="F44" s="75" t="inlineStr">
+        <is>
+          <t>Valid lookup source data</t>
+        </is>
+      </c>
+      <c r="G44" s="75" t="inlineStr">
+        <is>
+          <t>Lookup column gets expected value according to existing logic.</t>
+        </is>
+      </c>
+      <c r="H44" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I44" s="75" t="inlineStr"/>
+      <c r="J44" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K44" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L44" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M44" s="75" t="inlineStr"/>
+      <c r="N44" s="75" t="inlineStr">
+        <is>
+          <t>Valid lookup source data</t>
+        </is>
+      </c>
+      <c r="O44" s="75" t="inlineStr">
+        <is>
+          <t>Modify source/lookup value and refresh.</t>
+        </is>
+      </c>
+      <c r="P44" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="67">
+      <c r="A45" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B45" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C45" s="75" t="inlineStr">
+        <is>
+          <t>Verify manually refreshing does not trigger full Data Stream re-fetch</t>
+        </is>
+      </c>
+      <c r="D45" s="74" t="inlineStr">
+        <is>
+          <t>TC-43</t>
+        </is>
+      </c>
+      <c r="E45" s="75" t="inlineStr">
+        <is>
+          <t>Verify manually refreshing does not trigger full Data Stream re-fetch</t>
+        </is>
+      </c>
+      <c r="F45" s="75" t="inlineStr">
+        <is>
+          <t>Existing stream with external/source data</t>
+        </is>
+      </c>
+      <c r="G45" s="75" t="inlineStr">
+        <is>
+          <t>No complete re-fetch/upload/sync is initiated.</t>
+        </is>
+      </c>
+      <c r="H45" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I45" s="75" t="inlineStr"/>
+      <c r="J45" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K45" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L45" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M45" s="75" t="inlineStr"/>
+      <c r="N45" s="75" t="inlineStr">
+        <is>
+          <t>Existing stream with external/source data</t>
+        </is>
+      </c>
+      <c r="O45" s="75" t="inlineStr">
+        <is>
+          <t>Trigger Refresh Columns.</t>
+        </is>
+      </c>
+      <c r="P45" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="67">
+      <c r="A46" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B46" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C46" s="75" t="inlineStr">
+        <is>
+          <t>Verify manually refreshing does not modify raw/source records unnecessarily</t>
+        </is>
+      </c>
+      <c r="D46" s="74" t="inlineStr">
+        <is>
+          <t>TC-44</t>
+        </is>
+      </c>
+      <c r="E46" s="75" t="inlineStr">
+        <is>
+          <t>Verify manually refreshing does not modify raw/source records unnecessarily</t>
+        </is>
+      </c>
+      <c r="F46" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains raw and calculated fields</t>
+        </is>
+      </c>
+      <c r="G46" s="75" t="inlineStr">
+        <is>
+          <t>Only applicable Derived/Lookup values are recalculated/updated.</t>
+        </is>
+      </c>
+      <c r="H46" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I46" s="75" t="inlineStr"/>
+      <c r="J46" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K46" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L46" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M46" s="75" t="inlineStr"/>
+      <c r="N46" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains raw and calculated fields</t>
+        </is>
+      </c>
+      <c r="O46" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P46" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="67">
+      <c r="A47" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B47" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C47" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Derived Column create flow still works</t>
+        </is>
+      </c>
+      <c r="D47" s="74" t="inlineStr">
+        <is>
+          <t>TC-45</t>
+        </is>
+      </c>
+      <c r="E47" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Derived Column create flow still works</t>
+        </is>
+      </c>
+      <c r="F47" s="75" t="inlineStr">
+        <is>
+          <t>Create a new Derived Column</t>
+        </is>
+      </c>
+      <c r="G47" s="75" t="inlineStr">
+        <is>
+          <t>Existing processing behavior works as before.</t>
+        </is>
+      </c>
+      <c r="H47" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I47" s="75" t="inlineStr"/>
+      <c r="J47" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K47" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L47" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M47" s="75" t="inlineStr"/>
+      <c r="N47" s="75" t="inlineStr">
+        <is>
+          <t>Create a new Derived Column</t>
+        </is>
+      </c>
+      <c r="O47" s="75" t="inlineStr">
+        <is>
+          <t>Create and submit column.</t>
+        </is>
+      </c>
+      <c r="P47" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="67">
+      <c r="A48" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B48" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C48" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Derived Column edit flow still works</t>
+        </is>
+      </c>
+      <c r="D48" s="74" t="inlineStr">
+        <is>
+          <t>TC-46</t>
+        </is>
+      </c>
+      <c r="E48" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Derived Column edit flow still works</t>
+        </is>
+      </c>
+      <c r="F48" s="75" t="inlineStr">
+        <is>
+          <t>Existing Derived Column</t>
+        </is>
+      </c>
+      <c r="G48" s="75" t="inlineStr">
+        <is>
+          <t>Existing processing behavior works as before.</t>
+        </is>
+      </c>
+      <c r="H48" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I48" s="75" t="inlineStr"/>
+      <c r="J48" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K48" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L48" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M48" s="75" t="inlineStr"/>
+      <c r="N48" s="75" t="inlineStr">
+        <is>
+          <t>Existing Derived Column</t>
+        </is>
+      </c>
+      <c r="O48" s="75" t="inlineStr">
+        <is>
+          <t>Edit and submit column.</t>
+        </is>
+      </c>
+      <c r="P48" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="67">
+      <c r="A49" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B49" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C49" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Lookup Column create flow still works</t>
+        </is>
+      </c>
+      <c r="D49" s="74" t="inlineStr">
+        <is>
+          <t>TC-47</t>
+        </is>
+      </c>
+      <c r="E49" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Lookup Column create flow still works</t>
+        </is>
+      </c>
+      <c r="F49" s="75" t="inlineStr">
+        <is>
+          <t>Create Lookup Column</t>
+        </is>
+      </c>
+      <c r="G49" s="75" t="inlineStr">
+        <is>
+          <t>Existing processing behavior works as before.</t>
+        </is>
+      </c>
+      <c r="H49" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I49" s="75" t="inlineStr"/>
+      <c r="J49" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K49" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L49" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M49" s="75" t="inlineStr"/>
+      <c r="N49" s="75" t="inlineStr">
+        <is>
+          <t>Create Lookup Column</t>
+        </is>
+      </c>
+      <c r="O49" s="75" t="inlineStr">
+        <is>
+          <t>Create and submit.</t>
+        </is>
+      </c>
+      <c r="P49" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="67">
+      <c r="A50" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B50" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C50" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Lookup Column edit flow still works</t>
+        </is>
+      </c>
+      <c r="D50" s="74" t="inlineStr">
+        <is>
+          <t>TC-48</t>
+        </is>
+      </c>
+      <c r="E50" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Lookup Column edit flow still works</t>
+        </is>
+      </c>
+      <c r="F50" s="75" t="inlineStr">
+        <is>
+          <t>Existing Lookup Column</t>
+        </is>
+      </c>
+      <c r="G50" s="75" t="inlineStr">
+        <is>
+          <t>Existing processing behavior works as before.</t>
+        </is>
+      </c>
+      <c r="H50" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I50" s="75" t="inlineStr"/>
+      <c r="J50" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K50" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L50" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M50" s="75" t="inlineStr"/>
+      <c r="N50" s="75" t="inlineStr">
+        <is>
+          <t>Existing Lookup Column</t>
+        </is>
+      </c>
+      <c r="O50" s="75" t="inlineStr">
+        <is>
+          <t>Edit and submit.</t>
+        </is>
+      </c>
+      <c r="P50" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="67">
+      <c r="A51" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B51" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C51" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh when stream contains only Derived Columns</t>
+        </is>
+      </c>
+      <c r="D51" s="74" t="inlineStr">
+        <is>
+          <t>TC-49</t>
+        </is>
+      </c>
+      <c r="E51" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh when stream contains only Derived Columns</t>
+        </is>
+      </c>
+      <c r="F51" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 2+ Derived Columns and no Lookup</t>
+        </is>
+      </c>
+      <c r="G51" s="75" t="inlineStr">
+        <is>
+          <t>Derived columns are processed successfully; Lookup count is 0.</t>
+        </is>
+      </c>
+      <c r="H51" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I51" s="75" t="inlineStr"/>
+      <c r="J51" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K51" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L51" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M51" s="75" t="inlineStr"/>
+      <c r="N51" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 2+ Derived Columns and no Lookup</t>
+        </is>
+      </c>
+      <c r="O51" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P51" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1" s="67">
+      <c r="A52" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B52" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C52" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh when stream contains only Lookup Columns</t>
+        </is>
+      </c>
+      <c r="D52" s="74" t="inlineStr">
+        <is>
+          <t>TC-50</t>
+        </is>
+      </c>
+      <c r="E52" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh when stream contains only Lookup Columns</t>
+        </is>
+      </c>
+      <c r="F52" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 2+ Lookup Columns and no Derived</t>
+        </is>
+      </c>
+      <c r="G52" s="75" t="inlineStr">
+        <is>
+          <t>Lookup columns are processed successfully; Derived count is 0.</t>
+        </is>
+      </c>
+      <c r="H52" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I52" s="75" t="inlineStr"/>
+      <c r="J52" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K52" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L52" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M52" s="75" t="inlineStr"/>
+      <c r="N52" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 2+ Lookup Columns and no Derived</t>
+        </is>
+      </c>
+      <c r="O52" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P52" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1" s="67">
+      <c r="A53" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B53" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C53" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh for single Derived Column</t>
+        </is>
+      </c>
+      <c r="D53" s="74" t="inlineStr">
+        <is>
+          <t>TC-51</t>
+        </is>
+      </c>
+      <c r="E53" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh for single Derived Column</t>
+        </is>
+      </c>
+      <c r="F53" s="75" t="inlineStr">
+        <is>
+          <t>Stream has exactly 1 Derived Column</t>
+        </is>
+      </c>
+      <c r="G53" s="75" t="inlineStr">
+        <is>
+          <t>Single Derived Column is processed successfully.</t>
+        </is>
+      </c>
+      <c r="H53" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I53" s="75" t="inlineStr"/>
+      <c r="J53" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K53" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L53" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M53" s="75" t="inlineStr"/>
+      <c r="N53" s="75" t="inlineStr">
+        <is>
+          <t>Stream has exactly 1 Derived Column</t>
+        </is>
+      </c>
+      <c r="O53" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P53" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1" s="67">
+      <c r="A54" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B54" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C54" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh for single Lookup Column</t>
+        </is>
+      </c>
+      <c r="D54" s="74" t="inlineStr">
+        <is>
+          <t>TC-52</t>
+        </is>
+      </c>
+      <c r="E54" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh for single Lookup Column</t>
+        </is>
+      </c>
+      <c r="F54" s="75" t="inlineStr">
+        <is>
+          <t>Stream has exactly 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="G54" s="75" t="inlineStr">
+        <is>
+          <t>Single Lookup Column is processed successfully.</t>
+        </is>
+      </c>
+      <c r="H54" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I54" s="75" t="inlineStr"/>
+      <c r="J54" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K54" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L54" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M54" s="75" t="inlineStr"/>
+      <c r="N54" s="75" t="inlineStr">
+        <is>
+          <t>Stream has exactly 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="O54" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P54" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1" s="67">
+      <c r="A55" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B55" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C55" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh with zero records in Data Stream</t>
+        </is>
+      </c>
+      <c r="D55" s="74" t="inlineStr">
+        <is>
+          <t>TC-53</t>
+        </is>
+      </c>
+      <c r="E55" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh with zero records in Data Stream</t>
+        </is>
+      </c>
+      <c r="F55" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream exists but contains no records</t>
+        </is>
+      </c>
+      <c r="G55" s="75" t="inlineStr">
+        <is>
+          <t>Processing completes without error; counts reflect zero records processed/updated.</t>
+        </is>
+      </c>
+      <c r="H55" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I55" s="75" t="inlineStr"/>
+      <c r="J55" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K55" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L55" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M55" s="75" t="inlineStr"/>
+      <c r="N55" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream exists but contains no records</t>
+        </is>
+      </c>
+      <c r="O55" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P55" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1" s="67">
+      <c r="A56" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B56" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C56" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh with large dataset</t>
+        </is>
+      </c>
+      <c r="D56" s="74" t="inlineStr">
+        <is>
+          <t>TC-54</t>
+        </is>
+      </c>
+      <c r="E56" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh with large dataset</t>
+        </is>
+      </c>
+      <c r="F56" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream with large volume of records</t>
+        </is>
+      </c>
+      <c r="G56" s="75" t="inlineStr">
+        <is>
+          <t>Processing completes asynchronously without UI failure/time-out caused by synchronous processing.</t>
+        </is>
+      </c>
+      <c r="H56" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I56" s="75" t="inlineStr"/>
+      <c r="J56" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K56" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L56" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M56" s="75" t="inlineStr"/>
+      <c r="N56" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream with large volume of records</t>
+        </is>
+      </c>
+      <c r="O56" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P56" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1" s="67">
+      <c r="A57" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B57" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C57" s="75" t="inlineStr">
+        <is>
+          <t>Verify behavior when Derived/Lookup processing encounters invalid data</t>
+        </is>
+      </c>
+      <c r="D57" s="74" t="inlineStr">
+        <is>
+          <t>TC-55</t>
+        </is>
+      </c>
+      <c r="E57" s="75" t="inlineStr">
+        <is>
+          <t>Verify behavior when Derived/Lookup processing encounters invalid data</t>
+        </is>
+      </c>
+      <c r="F57" s="75" t="inlineStr">
+        <is>
+          <t>Dataset contains records that existing processing cannot calculate/resolve</t>
+        </is>
+      </c>
+      <c r="G57" s="75" t="inlineStr">
+        <is>
+          <t>Error handling follows existing Derived/Lookup processing behavior; unrelated records/columns are not incorrectly affected.</t>
+        </is>
+      </c>
+      <c r="H57" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I57" s="75" t="inlineStr"/>
+      <c r="J57" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K57" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L57" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M57" s="75" t="inlineStr"/>
+      <c r="N57" s="75" t="inlineStr">
+        <is>
+          <t>Dataset contains records that existing processing cannot calculate/resolve</t>
+        </is>
+      </c>
+      <c r="O57" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P57" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1" s="67">
+      <c r="A58" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B58" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C58" s="75" t="inlineStr">
+        <is>
+          <t>Verify action visibility updates after eligible column creation</t>
+        </is>
+      </c>
+      <c r="D58" s="74" t="inlineStr">
+        <is>
+          <t>TC-56</t>
+        </is>
+      </c>
+      <c r="E58" s="75" t="inlineStr">
+        <is>
+          <t>Verify action visibility updates after eligible column creation</t>
+        </is>
+      </c>
+      <c r="F58" s="75" t="inlineStr">
+        <is>
+          <t>Stream initially has no Derived/Lookup column</t>
+        </is>
+      </c>
+      <c r="G58" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns becomes available.</t>
+        </is>
+      </c>
+      <c r="H58" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I58" s="75" t="inlineStr"/>
+      <c r="J58" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K58" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L58" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M58" s="75" t="inlineStr"/>
+      <c r="N58" s="75" t="inlineStr">
+        <is>
+          <t>Stream initially has no Derived/Lookup column</t>
+        </is>
+      </c>
+      <c r="O58" s="75" t="inlineStr">
+        <is>
+          <t>1. Confirm action hidden.
+2. Create Derived Column.
+3. Return to Action menu.</t>
+        </is>
+      </c>
+      <c r="P58" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1" s="67">
+      <c r="A59" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B59" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C59" s="75" t="inlineStr">
+        <is>
+          <t>Verify action visibility updates after deleting all eligible columns</t>
+        </is>
+      </c>
+      <c r="D59" s="74" t="inlineStr">
+        <is>
+          <t>TC-57</t>
+        </is>
+      </c>
+      <c r="E59" s="75" t="inlineStr">
+        <is>
+          <t>Verify action visibility updates after deleting all eligible columns</t>
+        </is>
+      </c>
+      <c r="F59" s="75" t="inlineStr">
+        <is>
+          <t>Stream initially has Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="G59" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns is no longer displayed.</t>
+        </is>
+      </c>
+      <c r="H59" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I59" s="75" t="inlineStr"/>
+      <c r="J59" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K59" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L59" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M59" s="75" t="inlineStr"/>
+      <c r="N59" s="75" t="inlineStr">
+        <is>
+          <t>Stream initially has Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="O59" s="75" t="inlineStr">
+        <is>
+          <t>1. Confirm action visible.
+2. Remove all Derived/Lookup columns.
+3. Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P59" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1" s="67">
+      <c r="A60" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B60" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C60" s="75" t="inlineStr">
+        <is>
+          <t>Verify action remains hidden after deleting eligible columns from Key-Value stream</t>
+        </is>
+      </c>
+      <c r="D60" s="74" t="inlineStr">
+        <is>
+          <t>TC-58</t>
+        </is>
+      </c>
+      <c r="E60" s="75" t="inlineStr">
+        <is>
+          <t>Verify action remains hidden after deleting eligible columns from Key-Value stream</t>
+        </is>
+      </c>
+      <c r="F60" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value stream</t>
+        </is>
+      </c>
+      <c r="G60" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns remains unavailable.</t>
+        </is>
+      </c>
+      <c r="H60" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I60" s="75" t="inlineStr"/>
+      <c r="J60" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K60" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L60" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M60" s="75" t="inlineStr"/>
+      <c r="N60" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value stream</t>
+        </is>
+      </c>
+      <c r="O60" s="75" t="inlineStr">
+        <is>
+          <t>Remove/add eligible columns as applicable and reopen actions.</t>
+        </is>
+      </c>
+      <c r="P60" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1" s="67">
+      <c r="A61" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B61" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C61" s="75" t="inlineStr">
+        <is>
+          <t>Verify double-clicking Submit does not start duplicate processing</t>
+        </is>
+      </c>
+      <c r="D61" s="74" t="inlineStr">
+        <is>
+          <t>TC-59</t>
+        </is>
+      </c>
+      <c r="E61" s="75" t="inlineStr">
+        <is>
+          <t>Verify double-clicking Submit does not start duplicate processing</t>
+        </is>
+      </c>
+      <c r="F61" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G61" s="75" t="inlineStr">
+        <is>
+          <t>Only one processing operation is initiated.</t>
+        </is>
+      </c>
+      <c r="H61" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I61" s="75" t="inlineStr"/>
+      <c r="J61" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K61" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L61" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M61" s="75" t="inlineStr"/>
+      <c r="N61" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O61" s="75" t="inlineStr">
+        <is>
+          <t>Rapidly click Submit multiple times.</t>
+        </is>
+      </c>
+      <c r="P61" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1" s="67">
+      <c r="A62" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B62" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C62" s="75" t="inlineStr">
+        <is>
+          <t>Verify refreshing the page during processing does not corrupt processing state</t>
+        </is>
+      </c>
+      <c r="D62" s="74" t="inlineStr">
+        <is>
+          <t>TC-60</t>
+        </is>
+      </c>
+      <c r="E62" s="75" t="inlineStr">
+        <is>
+          <t>Verify refreshing the page during processing does not corrupt processing state</t>
+        </is>
+      </c>
+      <c r="F62" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is running</t>
+        </is>
+      </c>
+      <c r="G62" s="75" t="inlineStr">
+        <is>
+          <t>Backend processing continues according to existing async behavior; no duplicate process is created.</t>
+        </is>
+      </c>
+      <c r="H62" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I62" s="75" t="inlineStr"/>
+      <c r="J62" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K62" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L62" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M62" s="75" t="inlineStr"/>
+      <c r="N62" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is running</t>
+        </is>
+      </c>
+      <c r="O62" s="75" t="inlineStr">
+        <is>
+          <t>Refresh browser/page.</t>
+        </is>
+      </c>
+      <c r="P62" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1" s="67">
+      <c r="A63" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B63" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-07</t>
+        </is>
+      </c>
+      <c r="C63" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion modal values are actual and not hardcoded</t>
+        </is>
+      </c>
+      <c r="D63" s="74" t="inlineStr">
+        <is>
+          <t>TC-61</t>
+        </is>
+      </c>
+      <c r="E63" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion modal values are actual and not hardcoded</t>
+        </is>
+      </c>
+      <c r="F63" s="75" t="inlineStr">
+        <is>
+          <t>Use different datasets/column counts</t>
+        </is>
+      </c>
+      <c r="G63" s="75" t="inlineStr">
+        <is>
+          <t>Completion values change according to actual processing result.</t>
+        </is>
+      </c>
+      <c r="H63" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I63" s="75" t="inlineStr"/>
+      <c r="J63" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K63" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L63" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M63" s="75" t="inlineStr"/>
+      <c r="N63" s="75" t="inlineStr">
+        <is>
+          <t>Use different datasets/column counts</t>
+        </is>
+      </c>
+      <c r="O63" s="75" t="inlineStr">
+        <is>
+          <t>Trigger multiple refreshes with different counts/outcomes.</t>
+        </is>
+      </c>
+      <c r="P63" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1" s="67">
+      <c r="A64" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B64" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-07</t>
+        </is>
+      </c>
+      <c r="C64" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh does not affect another stream's computed values</t>
+        </is>
+      </c>
+      <c r="D64" s="74" t="inlineStr">
+        <is>
+          <t>TC-62</t>
+        </is>
+      </c>
+      <c r="E64" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh does not affect another stream's computed values</t>
+        </is>
+      </c>
+      <c r="F64" s="75" t="inlineStr">
+        <is>
+          <t>A and B have different source data and calculated results</t>
+        </is>
+      </c>
+      <c r="G64" s="75" t="inlineStr">
+        <is>
+          <t>B's Derived/Lookup values remain unchanged.</t>
+        </is>
+      </c>
+      <c r="H64" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I64" s="75" t="inlineStr"/>
+      <c r="J64" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K64" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L64" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M64" s="75" t="inlineStr"/>
+      <c r="N64" s="75" t="inlineStr">
+        <is>
+          <t>A and B have different source data and calculated results</t>
+        </is>
+      </c>
+      <c r="O64" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh only on A.</t>
+        </is>
+      </c>
+      <c r="P64" s="74" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
